--- a/preços.xlsx
+++ b/preços.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\albualv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DA2DA03-C5A7-4CB1-928B-90A550C99B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48536DBC-EC0B-4EDD-81F7-DC788EEE54EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-48120" yWindow="-1095" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3321,7 +3321,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3330,23 +3330,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3357,7 +3346,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -3365,33 +3354,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3699,16 +3670,16 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" t="s">
         <v>1091</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -3795,7 +3766,7 @@
       <c r="D7">
         <v>22.65</v>
       </c>
-      <c r="J7" s="2"/>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -11330,7 +11301,7 @@
       </c>
     </row>
     <row r="589" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E589" s="2"/>
+      <c r="E589" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/preços.xlsx
+++ b/preços.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\albualv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208D327C-433F-46BE-A2FD-AC12D685B4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8466C13B-673B-4479-9B8E-7288CCD3BB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-67470" yWindow="-1095" windowWidth="19440" windowHeight="14880" xr2:uid="{AE43EF37-9E80-4AA4-B8D8-6AD7DDD7CF31}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AE43EF37-9E80-4AA4-B8D8-6AD7DDD7CF31}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -1883,1693 +1883,1693 @@
   <volType type="realTimeData">
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...4293926781</v>
+        <v>#N/A Requesting Data...845196813</v>
         <stp/>
         <stp>BDP|18130380707939219871</stp>
         <tr r="D494" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4283254570</v>
+        <v>#N/A Requesting Data...3284098468</v>
         <stp/>
         <stp>BDP|13272921428474721656</stp>
         <tr r="D147" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4241315443</v>
+        <v>#N/A Requesting Data...1873496075</v>
         <stp/>
         <stp>BDP|17918545934148571367</stp>
         <tr r="D437" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4239469050</v>
+        <v>#N/A Requesting Data...2984345680</v>
         <stp/>
         <stp>BDP|10359585215779268705</stp>
         <tr r="D176" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4262079992</v>
+        <v>#N/A Requesting Data...996309480</v>
         <stp/>
         <stp>BDP|14609502577284537887</stp>
         <tr r="D214" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4239770709</v>
+        <v>#N/A Requesting Data...1321778682</v>
         <stp/>
         <stp>BDP|10523703117554535863</stp>
         <tr r="D486" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4243648993</v>
+        <v>#N/A Requesting Data...3977092062</v>
         <stp/>
         <stp>BDP|17880292975280720805</stp>
         <tr r="D357" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4257468269</v>
+        <v>#N/A Requesting Data...1011419140</v>
         <stp/>
         <stp>BDP|13387983340553002780</stp>
         <tr r="D14" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4244992759</v>
+        <v>#N/A Requesting Data...527394597</v>
         <stp/>
         <stp>BDP|15245981216285965267</stp>
         <tr r="D570" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4252675609</v>
+        <v>#N/A Requesting Data...881447449</v>
         <stp/>
         <stp>BDP|15113910186139780734</stp>
         <tr r="D395" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4249916059</v>
+        <v>#N/A Requesting Data...3095035827</v>
         <stp/>
         <stp>BDP|17006229196836462041</stp>
         <tr r="D521" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4253060148</v>
+        <v>#N/A Requesting Data...2967293252</v>
         <stp/>
         <stp>BDP|14733664627948255235</stp>
         <tr r="D524" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4257893448</v>
+        <v>#N/A Requesting Data...3605332529</v>
         <stp/>
         <stp>BDP|11475870723101102064</stp>
         <tr r="D455" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4277172528</v>
+        <v>#N/A Requesting Data...2194579279</v>
         <stp/>
         <stp>BDP|13138271577304613807</stp>
         <tr r="D541" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4271357450</v>
+        <v>#N/A Requesting Data...4093670922</v>
         <stp/>
         <stp>BDP|17357306299591446770</stp>
         <tr r="D384" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4287213222</v>
+        <v>#N/A Requesting Data...455538754</v>
         <stp/>
         <stp>BDP|15352968677290872022</stp>
         <tr r="D410" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4290508974</v>
+        <v>#N/A Requesting Data...3512016853</v>
         <stp/>
         <stp>BDP|12416029813160488899</stp>
         <tr r="D174" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4260181677</v>
+        <v>#N/A Requesting Data...1848839501</v>
         <stp/>
         <stp>BDP|10792138599862271139</stp>
         <tr r="D261" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4285740441</v>
+        <v>#N/A Requesting Data...1854140126</v>
         <stp/>
         <stp>BDP|12207032838648321251</stp>
         <tr r="D433" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4267786345</v>
+        <v>#N/A Requesting Data...4294837459</v>
         <stp/>
         <stp>BDP|10348758089856561248</stp>
         <tr r="D381" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4272584154</v>
+        <v>#N/A Requesting Data...2923750813</v>
         <stp/>
         <stp>BDP|13101297941857035980</stp>
         <tr r="D181" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4277401166</v>
+        <v>#N/A Requesting Data...1712403323</v>
         <stp/>
         <stp>BDP|11113578372618316043</stp>
         <tr r="D6" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4292169708</v>
+        <v>#N/A Requesting Data...2141122064</v>
         <stp/>
         <stp>BDP|17344867564695058726</stp>
         <tr r="D439" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4266354063</v>
+        <v>#N/A Requesting Data...2742741782</v>
         <stp/>
         <stp>BDP|11064713536247181933</stp>
         <tr r="D130" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4265319832</v>
+        <v>#N/A Requesting Data...1262013010</v>
         <stp/>
         <stp>BDP|15033921509094675381</stp>
         <tr r="D277" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4273786453</v>
+        <v>#N/A Requesting Data...2109462268</v>
         <stp/>
         <stp>BDP|18281415759177910546</stp>
         <tr r="D152" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4284662072</v>
+        <v>#N/A Requesting Data...2959716967</v>
         <stp/>
         <stp>BDP|18134660038734956219</stp>
         <tr r="D345" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4287299493</v>
+        <v>#N/A Requesting Data...1002056158</v>
         <stp/>
         <stp>BDP|10843064325063376936</stp>
         <tr r="D145" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4273563279</v>
+        <v>#N/A Requesting Data...1694248951</v>
         <stp/>
         <stp>BDP|18159706965541727098</stp>
         <tr r="D581" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4275215365</v>
+        <v>#N/A Requesting Data...1817242845</v>
         <stp/>
         <stp>BDP|12317460689491914796</stp>
         <tr r="D448" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4272826652</v>
+        <v>#N/A Requesting Data...1047983089</v>
         <stp/>
         <stp>BDP|15079925338093389470</stp>
         <tr r="D119" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4286790797</v>
+        <v>#N/A Requesting Data...703818452</v>
         <stp/>
         <stp>BDP|13497368782414632485</stp>
         <tr r="D30" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4288609291</v>
+        <v>#N/A Requesting Data...801858764</v>
         <stp/>
         <stp>BDP|11370635344389212282</stp>
         <tr r="D350" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4286651266</v>
+        <v>#N/A Requesting Data...4121488266</v>
         <stp/>
         <stp>BDP|15008276610608798613</stp>
         <tr r="D255" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4292529848</v>
+        <v>#N/A Requesting Data...3555848641</v>
         <stp/>
         <stp>BDP|17413651789491811050</stp>
         <tr r="D478" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4292918265</v>
+        <v>#N/A Requesting Data...4009065602</v>
         <stp/>
         <stp>BDP|11780792104807847973</stp>
         <tr r="D47" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4288497894</v>
+        <v>#N/A Requesting Data...1889037209</v>
         <stp/>
         <stp>BDP|14805141504898435585</stp>
         <tr r="D66" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4294009960</v>
+        <v>#N/A Requesting Data...1249413206</v>
         <stp/>
         <stp>BDP|10575312694051436305</stp>
         <tr r="D403" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4287335256</v>
+        <v>#N/A Requesting Data...2328779699</v>
         <stp/>
         <stp>BDP|10700940686560729962</stp>
         <tr r="D376" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4289930916</v>
+        <v>#N/A Requesting Data...1182520285</v>
         <stp/>
         <stp>BDP|11792873564044596357</stp>
         <tr r="D538" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4292976840</v>
+        <v>#N/A Requesting Data...2040873882</v>
         <stp/>
         <stp>BDP|17679317681626517244</stp>
         <tr r="D554" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4291875538</v>
+        <v>#N/A Requesting Data...3817911628</v>
         <stp/>
         <stp>BDP|10397638545702181838</stp>
         <tr r="D411" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4291608191</v>
+        <v>#N/A Requesting Data...3640755696</v>
         <stp/>
         <stp>BDP|15630850427663880551</stp>
         <tr r="D389" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4292213167</v>
+        <v>#N/A Requesting Data...1531328028</v>
         <stp/>
         <stp>BDP|10299434835367932948</stp>
         <tr r="D110" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4294569551</v>
+        <v>#N/A Requesting Data...2575157926</v>
         <stp/>
         <stp>BDP|12865536850258628375</stp>
         <tr r="D526" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4294162684</v>
+        <v>#N/A Requesting Data...3270818514</v>
         <stp/>
         <stp>BDP|14709709392313112094</stp>
         <tr r="D253" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1475317345</v>
+        <v>#N/A Requesting Data...1616466185</v>
         <stp/>
         <stp>BDP|10688999501917520745</stp>
         <tr r="D498" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...826468233</v>
+        <v>#N/A Requesting Data...2365787816</v>
         <stp/>
         <stp>BDP|17246154003606854923</stp>
         <tr r="D353" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...858721795</v>
+        <v>#N/A Requesting Data...4240716649</v>
         <stp/>
         <stp>BDP|11718513388440615598</stp>
         <tr r="D169" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2038333679</v>
+        <v>#N/A Requesting Data...1162331299</v>
         <stp/>
         <stp>BDP|10074279046239945688</stp>
         <tr r="D135" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4148698127</v>
+        <v>#N/A Requesting Data...3826222835</v>
         <stp/>
         <stp>BDP|14594546126098525216</stp>
         <tr r="D471" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...297164310</v>
+        <v>#N/A Requesting Data...3249209292</v>
         <stp/>
         <stp>BDP|15849798574884762819</stp>
         <tr r="D334" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...720050608</v>
+        <v>#N/A Requesting Data...1928189493</v>
         <stp/>
         <stp>BDP|11385921760102622516</stp>
         <tr r="D272" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2058155375</v>
+        <v>#N/A Requesting Data...2682497836</v>
         <stp/>
         <stp>BDP|18361103979421662146</stp>
         <tr r="D291" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1047025747</v>
+        <v>#N/A Requesting Data...2263930252</v>
         <stp/>
         <stp>BDP|12330990757589669935</stp>
         <tr r="D232" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3987630809</v>
+        <v>#N/A Requesting Data...2030573119</v>
         <stp/>
         <stp>BDP|13701082089486547385</stp>
         <tr r="D569" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...828593094</v>
+        <v>#N/A Requesting Data...2397242235</v>
         <stp/>
         <stp>BDP|12833360906528189729</stp>
         <tr r="D175" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1414837647</v>
+        <v>#N/A Requesting Data...3877252952</v>
         <stp/>
         <stp>BDP|12694354178120007808</stp>
         <tr r="D36" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...234960978</v>
+        <v>#N/A Requesting Data...743703974</v>
         <stp/>
         <stp>BDP|18307045953337951479</stp>
         <tr r="D462" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2377328956</v>
+        <v>#N/A Requesting Data...2797108442</v>
         <stp/>
         <stp>BDP|17090317293102876104</stp>
         <tr r="D457" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3172691798</v>
+        <v>#N/A Requesting Data...2322747181</v>
         <stp/>
         <stp>BDP|12546426298205256424</stp>
         <tr r="D196" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1075968026</v>
+        <v>#N/A Requesting Data...1583736230</v>
         <stp/>
         <stp>BDP|15269980654434519350</stp>
         <tr r="D211" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3832898128</v>
+        <v>#N/A Requesting Data...3774762844</v>
         <stp/>
         <stp>BDP|12292199959648622054</stp>
         <tr r="D208" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3334108887</v>
+        <v>#N/A Requesting Data...3196027743</v>
         <stp/>
         <stp>BDP|11145590832038972135</stp>
         <tr r="D408" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1743512554</v>
+        <v>#N/A Requesting Data...2446422816</v>
         <stp/>
         <stp>BDP|18062401136285475426</stp>
         <tr r="D355" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3952840051</v>
+        <v>#N/A Requesting Data...1271780457</v>
         <stp/>
         <stp>BDP|10020961262818685911</stp>
         <tr r="D464" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...928056520</v>
+        <v>#N/A Requesting Data...2693181673</v>
         <stp/>
         <stp>BDP|15054492373699905119</stp>
         <tr r="D161" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1884661630</v>
+        <v>#N/A Requesting Data...4236362866</v>
         <stp/>
         <stp>BDP|10366387513528886454</stp>
         <tr r="D223" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...923937713</v>
+        <v>#N/A Requesting Data...3704619294</v>
         <stp/>
         <stp>BDP|16026093729018083259</stp>
         <tr r="D588" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...568220586</v>
+        <v>#N/A Requesting Data...3358243109</v>
         <stp/>
         <stp>BDP|15643786772923120898</stp>
         <tr r="D513" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4141406300</v>
+        <v>#N/A Requesting Data...3956798502</v>
         <stp/>
         <stp>BDP|13950831853669683875</stp>
         <tr r="D141" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1287158820</v>
+        <v>#N/A Requesting Data...1064687645</v>
         <stp/>
         <stp>BDP|10203716481098356891</stp>
         <tr r="D378" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...484217641</v>
+        <v>#N/A Requesting Data...4013863396</v>
         <stp/>
         <stp>BDP|16081571685223984708</stp>
         <tr r="D217" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3011806630</v>
+        <v>#N/A Requesting Data...2729285370</v>
         <stp/>
         <stp>BDP|12087348692815588284</stp>
         <tr r="D506" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2025218694</v>
+        <v>#N/A Requesting Data...3042175073</v>
         <stp/>
         <stp>BDP|15422832002240955212</stp>
         <tr r="D220" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3100326309</v>
+        <v>#N/A Requesting Data...4014475970</v>
         <stp/>
         <stp>BDP|16991874719721255196</stp>
         <tr r="D151" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3525703818</v>
+        <v>#N/A Requesting Data...2603519266</v>
         <stp/>
         <stp>BDP|15563754854189180195</stp>
         <tr r="D111" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...107946942</v>
+        <v>#N/A Requesting Data...2930078725</v>
         <stp/>
         <stp>BDP|18233671528421709260</stp>
         <tr r="D2" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...616278068</v>
+        <v>#N/A Requesting Data...761446434</v>
         <stp/>
         <stp>BDP|12347098919639931548</stp>
         <tr r="D468" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3792720402</v>
+        <v>#N/A Requesting Data...4184641778</v>
         <stp/>
         <stp>BDP|15040650453540137969</stp>
         <tr r="D33" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...80008603</v>
+        <v>#N/A Requesting Data...3692372416</v>
         <stp/>
         <stp>BDP|14713044783876268534</stp>
         <tr r="D112" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1537085257</v>
+        <v>#N/A Requesting Data...1256324095</v>
         <stp/>
         <stp>BDP|11777964681768087705</stp>
         <tr r="D163" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1090276174</v>
+        <v>#N/A Requesting Data...3725324274</v>
         <stp/>
         <stp>BDP|10072918796386593924</stp>
         <tr r="D349" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1200035050</v>
+        <v>#N/A Requesting Data...1115656274</v>
         <stp/>
         <stp>BDP|12579789340769757796</stp>
         <tr r="D201" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1086014828</v>
+        <v>#N/A Requesting Data...3398817022</v>
         <stp/>
         <stp>BDP|17186185790582225282</stp>
         <tr r="D360" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2115095736</v>
+        <v>#N/A Requesting Data...548998680</v>
         <stp/>
         <stp>BDP|11186736915029448107</stp>
         <tr r="D467" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2176822493</v>
+        <v>#N/A Requesting Data...3090964586</v>
         <stp/>
         <stp>BDP|18445632104784101507</stp>
         <tr r="D74" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3255757163</v>
+        <v>#N/A Requesting Data...786900054</v>
         <stp/>
         <stp>BDP|13750348676750788876</stp>
         <tr r="D241" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...615178339</v>
+        <v>#N/A Requesting Data...1390403263</v>
         <stp/>
         <stp>BDP|12648313194561206588</stp>
         <tr r="D224" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...759735244</v>
+        <v>#N/A Requesting Data...2878484075</v>
         <stp/>
         <stp>BDP|11255287860608146111</stp>
         <tr r="D247" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2515817842</v>
+        <v>#N/A Requesting Data...4273764602</v>
         <stp/>
         <stp>BDP|11060498389153524295</stp>
         <tr r="D41" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1918985178</v>
+        <v>#N/A Requesting Data...3527096097</v>
         <stp/>
         <stp>BDP|15082279357316840845</stp>
         <tr r="D82" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2657383613</v>
+        <v>#N/A Requesting Data...2083810035</v>
         <stp/>
         <stp>BDP|13018792333298038367</stp>
         <tr r="D337" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4125089680</v>
+        <v>#N/A Requesting Data...2881376792</v>
         <stp/>
         <stp>BDP|16034078399554387724</stp>
         <tr r="D67" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...931909575</v>
+        <v>#N/A Requesting Data...1720631040</v>
         <stp/>
         <stp>BDP|11017677302663987838</stp>
         <tr r="D330" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1292017923</v>
+        <v>#N/A Requesting Data...2958201839</v>
         <stp/>
         <stp>BDP|16288956325890435193</stp>
         <tr r="D428" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...788577086</v>
+        <v>#N/A Requesting Data...2297146983</v>
         <stp/>
         <stp>BDP|16508737268469692262</stp>
         <tr r="D394" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2400073615</v>
+        <v>#N/A Requesting Data...3597959931</v>
         <stp/>
         <stp>BDP|17489309769416190823</stp>
         <tr r="D35" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3250568827</v>
+        <v>#N/A Requesting Data...1042621257</v>
         <stp/>
         <stp>BDP|10327924102764509176</stp>
         <tr r="D259" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3717918654</v>
+        <v>#N/A Requesting Data...1847481726</v>
         <stp/>
         <stp>BDP|14214668141508133267</stp>
         <tr r="D319" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...671358915</v>
+        <v>#N/A Requesting Data...1035657903</v>
         <stp/>
         <stp>BDP|10159155091567349325</stp>
         <tr r="D73" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...450219310</v>
+        <v>#N/A Requesting Data...1537535308</v>
         <stp/>
         <stp>BDP|18219580234070987204</stp>
         <tr r="D335" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3642384534</v>
+        <v>#N/A Requesting Data...2003334957</v>
         <stp/>
         <stp>BDP|10096541094276701606</stp>
         <tr r="D71" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2232715081</v>
+        <v>#N/A Requesting Data...750704587</v>
         <stp/>
         <stp>BDP|15716824664276581128</stp>
         <tr r="D18" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...940298152</v>
+        <v>#N/A Requesting Data...2618009571</v>
         <stp/>
         <stp>BDP|11650399697931413745</stp>
         <tr r="D320" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2840285160</v>
+        <v>#N/A Requesting Data...1955841158</v>
         <stp/>
         <stp>BDP|14984926737482124165</stp>
         <tr r="D72" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3335989053</v>
+        <v>#N/A Requesting Data...1036160902</v>
         <stp/>
         <stp>BDP|17736931112035313788</stp>
         <tr r="D555" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...463479745</v>
+        <v>#N/A Requesting Data...2779789880</v>
         <stp/>
         <stp>BDP|11415978518523302750</stp>
         <tr r="D19" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2612824718</v>
+        <v>#N/A Requesting Data...979749400</v>
         <stp/>
         <stp>BDP|10594587902099698143</stp>
         <tr r="D172" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4139597743</v>
+        <v>#N/A Requesting Data...1387380253</v>
         <stp/>
         <stp>BDP|12842945982549795755</stp>
         <tr r="D361" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1291405586</v>
+        <v>#N/A Requesting Data...3617667438</v>
         <stp/>
         <stp>BDP|13326252000554807827</stp>
         <tr r="D343" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1986224649</v>
+        <v>#N/A Requesting Data...2292232449</v>
         <stp/>
         <stp>BDP|11267866972967012490</stp>
         <tr r="D432" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2073278780</v>
+        <v>#N/A Requesting Data...978198390</v>
         <stp/>
         <stp>BDP|10145694666555196814</stp>
         <tr r="D116" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3332571566</v>
+        <v>#N/A Requesting Data...1951356101</v>
         <stp/>
         <stp>BDP|18091252167988074906</stp>
         <tr r="D310" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3624833729</v>
+        <v>#N/A Requesting Data...852740360</v>
         <stp/>
         <stp>BDP|16779559517576091909</stp>
         <tr r="D164" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1581837352</v>
+        <v>#N/A Requesting Data...2650517823</v>
         <stp/>
         <stp>BDP|18308906582367594305</stp>
         <tr r="D547" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2755272413</v>
+        <v>#N/A Requesting Data...691477009</v>
         <stp/>
         <stp>BDP|11485193597021552588</stp>
         <tr r="D419" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3200258340</v>
+        <v>#N/A Requesting Data...2645720230</v>
         <stp/>
         <stp>BDP|17671531230038389404</stp>
         <tr r="D562" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2606349341</v>
+        <v>#N/A Requesting Data...3471522783</v>
         <stp/>
         <stp>BDP|17944671009275579949</stp>
         <tr r="D485" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...939444591</v>
+        <v>#N/A Requesting Data...3572509709</v>
         <stp/>
         <stp>BDP|12888920157895325971</stp>
         <tr r="D492" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1881849547</v>
+        <v>#N/A Requesting Data...2218794005</v>
         <stp/>
         <stp>BDP|14384728205156821752</stp>
         <tr r="D558" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2645614121</v>
+        <v>#N/A Requesting Data...3863685062</v>
         <stp/>
         <stp>BDP|12956955985050388128</stp>
         <tr r="D499" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3497640570</v>
+        <v>#N/A Requesting Data...2567045317</v>
         <stp/>
         <stp>BDP|14207353745486106780</stp>
         <tr r="D546" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...757127865</v>
+        <v>#N/A Requesting Data...2872826941</v>
         <stp/>
         <stp>BDP|15487370700661807577</stp>
         <tr r="D563" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1180894351</v>
+        <v>#N/A Requesting Data...565122467</v>
         <stp/>
         <stp>BDP|16390891586697091303</stp>
         <tr r="D386" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2035901526</v>
+        <v>#N/A Requesting Data...1788465738</v>
         <stp/>
         <stp>BDP|13914702938727660298</stp>
         <tr r="D158" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...844449919</v>
+        <v>#N/A Requesting Data...2402454812</v>
         <stp/>
         <stp>BDP|12205733039972473628</stp>
         <tr r="D245" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2935205457</v>
+        <v>#N/A Requesting Data...1506894247</v>
         <stp/>
         <stp>BDP|13323312610317153427</stp>
         <tr r="D365" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4005656382</v>
+        <v>#N/A Requesting Data...1650875178</v>
         <stp/>
         <stp>BDP|15485684705274090592</stp>
         <tr r="D314" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1599230820</v>
+        <v>#N/A Requesting Data...1645293976</v>
         <stp/>
         <stp>BDP|12381802294931724032</stp>
         <tr r="D63" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3812060938</v>
+        <v>#N/A Requesting Data...3658344430</v>
         <stp/>
         <stp>BDP|16128417127416132452</stp>
         <tr r="D143" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2735535282</v>
+        <v>#N/A Requesting Data...1137386623</v>
         <stp/>
         <stp>BDP|13314951595610858199</stp>
         <tr r="D396" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2999882232</v>
+        <v>#N/A Requesting Data...1233688722</v>
         <stp/>
         <stp>BDP|10647601262710524232</stp>
         <tr r="D22" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2269525378</v>
+        <v>#N/A Requesting Data...1060978346</v>
         <stp/>
         <stp>BDP|12170321605385703640</stp>
         <tr r="D586" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4058421348</v>
+        <v>#N/A Requesting Data...2746999134</v>
         <stp/>
         <stp>BDP|10251271759446819315</stp>
         <tr r="D321" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...769037024</v>
+        <v>#N/A Requesting Data...599024482</v>
         <stp/>
         <stp>BDP|14749102142477276435</stp>
         <tr r="D252" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1982707346</v>
+        <v>#N/A Requesting Data...3286699986</v>
         <stp/>
         <stp>BDP|13097137766463547571</stp>
         <tr r="D166" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3370752758</v>
+        <v>#N/A Requesting Data...2385891101</v>
         <stp/>
         <stp>BDP|10022795212553512788</stp>
         <tr r="D415" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...447752658</v>
+        <v>#N/A Requesting Data...2349029774</v>
         <stp/>
         <stp>BDP|11670267993698035058</stp>
         <tr r="D226" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...156835183</v>
+        <v>#N/A Requesting Data...1252724335</v>
         <stp/>
         <stp>BDP|10910478370500958118</stp>
         <tr r="D26" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1525168199</v>
+        <v>#N/A Requesting Data...4123672215</v>
         <stp/>
         <stp>BDP|10811766400763548723</stp>
         <tr r="D391" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...587545161</v>
+        <v>#N/A Requesting Data...3534592143</v>
         <stp/>
         <stp>BDP|10703131378317158258</stp>
         <tr r="D385" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2453294063</v>
+        <v>#N/A Requesting Data...3874225169</v>
         <stp/>
         <stp>BDP|15027715085688829177</stp>
         <tr r="D236" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2279950247</v>
+        <v>#N/A Requesting Data...1990211131</v>
         <stp/>
         <stp>BDP|11939128969835106094</stp>
         <tr r="D113" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...878662399</v>
+        <v>#N/A Requesting Data...2926906747</v>
         <stp/>
         <stp>BDP|10715237403329285889</stp>
         <tr r="D535" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2997664989</v>
+        <v>#N/A Requesting Data...3000536374</v>
         <stp/>
         <stp>BDP|16300745519763116031</stp>
         <tr r="D533" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...937755425</v>
+        <v>#N/A Requesting Data...736506567</v>
         <stp/>
         <stp>BDP|14757059765145947416</stp>
         <tr r="D495" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2314274122</v>
+        <v>#N/A Requesting Data...1958450299</v>
         <stp/>
         <stp>BDP|15233694536795741657</stp>
         <tr r="D296" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3296421743</v>
+        <v>#N/A Requesting Data...1554466274</v>
         <stp/>
         <stp>BDP|10868308007497694781</stp>
         <tr r="D212" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3079915394</v>
+        <v>#N/A Requesting Data...3710254636</v>
         <stp/>
         <stp>BDP|13576587303225983020</stp>
         <tr r="D393" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...790608582</v>
+        <v>#N/A Requesting Data...1326651565</v>
         <stp/>
         <stp>BDP|13233798871599870978</stp>
         <tr r="D501" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2214829915</v>
+        <v>#N/A Requesting Data...1268667170</v>
         <stp/>
         <stp>BDP|16302534045340242427</stp>
         <tr r="D463" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4245023526</v>
+        <v>#N/A Requesting Data...1444184123</v>
         <stp/>
         <stp>BDP|11236970886847641416</stp>
         <tr r="D139" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...721636264</v>
+        <v>#N/A Requesting Data...3925199443</v>
         <stp/>
         <stp>BDP|11250544236700405402</stp>
         <tr r="D445" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1705060516</v>
+        <v>#N/A Requesting Data...2497886482</v>
         <stp/>
         <stp>BDP|13104492506126068287</stp>
         <tr r="D242" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1074734317</v>
+        <v>#N/A Requesting Data...3804055798</v>
         <stp/>
         <stp>BDP|15151413762184373390</stp>
         <tr r="D465" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2847133130</v>
+        <v>#N/A Requesting Data...2199045538</v>
         <stp/>
         <stp>BDP|13108093994608039241</stp>
         <tr r="D88" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3126057613</v>
+        <v>#N/A Requesting Data...2047791706</v>
         <stp/>
         <stp>BDP|13905897685930790390</stp>
         <tr r="D185" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2820364927</v>
+        <v>#N/A Requesting Data...1228262865</v>
         <stp/>
         <stp>BDP|13283842173839337592</stp>
         <tr r="D559" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3650621161</v>
+        <v>#N/A Requesting Data...4161698311</v>
         <stp/>
         <stp>BDP|15450981830706451974</stp>
         <tr r="D234" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4054346424</v>
+        <v>#N/A Requesting Data...4109208583</v>
         <stp/>
         <stp>BDP|17562294566076414517</stp>
         <tr r="D539" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4163856979</v>
+        <v>#N/A Requesting Data...965160251</v>
         <stp/>
         <stp>BDP|10784779746532370148</stp>
         <tr r="D412" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...743264866</v>
+        <v>#N/A Requesting Data...3318882829</v>
         <stp/>
         <stp>BDP|16994081820262216629</stp>
         <tr r="D32" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3839448249</v>
+        <v>#N/A Requesting Data...2968014187</v>
         <stp/>
         <stp>BDP|10522890148265570913</stp>
         <tr r="D488" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2879136229</v>
+        <v>#N/A Requesting Data...3512951442</v>
         <stp/>
         <stp>BDP|15637724752244563349</stp>
         <tr r="D483" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2986185535</v>
+        <v>#N/A Requesting Data...1707808134</v>
         <stp/>
         <stp>BDP|15760863175538200215</stp>
         <tr r="D179" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1647227078</v>
+        <v>#N/A Requesting Data...2312593300</v>
         <stp/>
         <stp>BDP|16687246334372728579</stp>
         <tr r="D525" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2583168049</v>
+        <v>#N/A Requesting Data...2712782779</v>
         <stp/>
         <stp>BDP|11208501170434598718</stp>
         <tr r="D96" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3156575766</v>
+        <v>#N/A Requesting Data...2830945904</v>
         <stp/>
         <stp>BDP|12609542046271408398</stp>
         <tr r="D65" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3977370529</v>
+        <v>#N/A Requesting Data...2685901648</v>
         <stp/>
         <stp>BDP|15469027550349877877</stp>
         <tr r="D235" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3230246870</v>
+        <v>#N/A Requesting Data...3801041566</v>
         <stp/>
         <stp>BDP|11367997991317820785</stp>
         <tr r="D263" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1103534301</v>
+        <v>#N/A Requesting Data...1001457800</v>
         <stp/>
         <stp>BDP|12820117795702003977</stp>
         <tr r="D129" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2051564298</v>
+        <v>#N/A Requesting Data...2600161228</v>
         <stp/>
         <stp>BDP|15264991111529252528</stp>
         <tr r="D540" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1167888948</v>
+        <v>#N/A Requesting Data...2316649650</v>
         <stp/>
         <stp>BDP|12366900629571912994</stp>
         <tr r="D454" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3707898041</v>
+        <v>#N/A Requesting Data...3822898243</v>
         <stp/>
         <stp>BDP|16169615241666922345</stp>
         <tr r="D532" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3645494402</v>
+        <v>#N/A Requesting Data...1527683829</v>
         <stp/>
         <stp>BDP|13726011124796725694</stp>
         <tr r="D528" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3335172179</v>
+        <v>#N/A Requesting Data...1569303749</v>
         <stp/>
         <stp>BDP|16894163460907170703</stp>
         <tr r="D413" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1572627280</v>
+        <v>#N/A Requesting Data...3131379235</v>
         <stp/>
         <stp>BDP|13702737840426277786</stp>
         <tr r="D204" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1842447627</v>
+        <v>#N/A Requesting Data...3755371417</v>
         <stp/>
         <stp>BDP|10153802031663337929</stp>
         <tr r="D504" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3118900879</v>
+        <v>#N/A Requesting Data...4020748133</v>
         <stp/>
         <stp>BDP|13066034642876576054</stp>
         <tr r="D520" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2359042675</v>
+        <v>#N/A Requesting Data...1648435177</v>
         <stp/>
         <stp>BDP|16340699605622724396</stp>
         <tr r="D4" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2624063358</v>
+        <v>#N/A Requesting Data...2558874003</v>
         <stp/>
         <stp>BDP|17645679353424750150</stp>
         <tr r="D549" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3355809456</v>
+        <v>#N/A Requesting Data...1998142240</v>
         <stp/>
         <stp>BDP|14320582714404582590</stp>
         <tr r="D327" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1865382338</v>
+        <v>#N/A Requesting Data...2620070491</v>
         <stp/>
         <stp>BDP|12374037063087258227</stp>
         <tr r="D92" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1961479438</v>
+        <v>#N/A Requesting Data...3638310471</v>
         <stp/>
         <stp>BDP|18021314433950117962</stp>
         <tr r="D305" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2858539754</v>
+        <v>#N/A Requesting Data...1780523732</v>
         <stp/>
         <stp>BDP|16661746631460270341</stp>
         <tr r="D59" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...884523253</v>
+        <v>#N/A Requesting Data...1000641628</v>
         <stp/>
         <stp>BDP|16139009584989735677</stp>
         <tr r="D493" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4194619368</v>
+        <v>#N/A Requesting Data...3809683780</v>
         <stp/>
         <stp>BDP|18392111986674204411</stp>
         <tr r="D99" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2173438595</v>
+        <v>#N/A Requesting Data...3590409250</v>
         <stp/>
         <stp>BDP|13266165674551253555</stp>
         <tr r="D584" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2153275239</v>
+        <v>#N/A Requesting Data...4008144852</v>
         <stp/>
         <stp>BDP|16538600821372065125</stp>
         <tr r="D140" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2055122335</v>
+        <v>#N/A Requesting Data...3543159855</v>
         <stp/>
         <stp>BDP|12236361903354152400</stp>
         <tr r="D198" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2615087694</v>
+        <v>#N/A Requesting Data...3255487949</v>
         <stp/>
         <stp>BDP|11972320470551574278</stp>
         <tr r="D57" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...884870706</v>
+        <v>#N/A Requesting Data...3735321759</v>
         <stp/>
         <stp>BDP|13438025448194422534</stp>
         <tr r="D351" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3715151232</v>
+        <v>#N/A Requesting Data...2585647723</v>
         <stp/>
         <stp>BDP|14650585776218060810</stp>
         <tr r="D348" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...848094696</v>
+        <v>#N/A Requesting Data...4176609527</v>
         <stp/>
         <stp>BDP|15485576618802696566</stp>
         <tr r="D108" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...632904106</v>
+        <v>#N/A Requesting Data...3099239360</v>
         <stp/>
         <stp>BDP|17192821848568156517</stp>
         <tr r="D451" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2036391659</v>
+        <v>#N/A Requesting Data...2007251837</v>
         <stp/>
         <stp>BDP|11028997372759591059</stp>
         <tr r="D449" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4261975142</v>
+        <v>#N/A Requesting Data...773355572</v>
         <stp/>
         <stp>BDP|12928854088544978010</stp>
         <tr r="D168" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3740443856</v>
+        <v>#N/A Requesting Data...2540697290</v>
         <stp/>
         <stp>BDP|11858753862823839583</stp>
         <tr r="D222" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...792239672</v>
+        <v>#N/A Requesting Data...2798421975</v>
         <stp/>
         <stp>BDP|18088474311458072398</stp>
         <tr r="D338" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1781597299</v>
+        <v>#N/A Requesting Data...1057992774</v>
         <stp/>
         <stp>BDP|10554615992340870911</stp>
         <tr r="D162" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1798394521</v>
+        <v>#N/A Requesting Data...3295218228</v>
         <stp/>
         <stp>BDP|11158599031040508123</stp>
         <tr r="D49" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...626916591</v>
+        <v>#N/A Requesting Data...3158954611</v>
         <stp/>
         <stp>BDP|16903117249272927768</stp>
         <tr r="D153" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1911458936</v>
+        <v>#N/A Requesting Data...855328054</v>
         <stp/>
         <stp>BDP|16528149873400913659</stp>
         <tr r="D496" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...363080495</v>
+        <v>#N/A Requesting Data...2782810477</v>
         <stp/>
         <stp>BDP|14477493111353519489</stp>
         <tr r="D157" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...807721297</v>
+        <v>#N/A Requesting Data...3182097460</v>
         <stp/>
         <stp>BDP|12676421250643548602</stp>
         <tr r="D480" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2806464969</v>
+        <v>#N/A Requesting Data...2931264871</v>
         <stp/>
         <stp>BDP|12834375803074882344</stp>
         <tr r="D227" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1695220935</v>
+        <v>#N/A Requesting Data...1318719237</v>
         <stp/>
         <stp>BDP|14033553395358471644</stp>
         <tr r="D367" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...306403089</v>
+        <v>#N/A Requesting Data...2145546481</v>
         <stp/>
         <stp>BDP|12730229413000274748</stp>
         <tr r="D401" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3390933205</v>
+        <v>#N/A Requesting Data...1687545334</v>
         <stp/>
         <stp>BDP|14573204369812726486</stp>
         <tr r="D251" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4040410908</v>
+        <v>#N/A Requesting Data...4229595743</v>
         <stp/>
         <stp>BDP|12278073778620764393</stp>
         <tr r="D331" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1390161331</v>
+        <v>#N/A Requesting Data...1933887138</v>
         <stp/>
         <stp>BDP|15357110614897143423</stp>
         <tr r="D28" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4044496416</v>
+        <v>#N/A Requesting Data...2056484927</v>
         <stp/>
         <stp>BDP|11629781892348830116</stp>
         <tr r="D552" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...799979019</v>
+        <v>#N/A Requesting Data...3268149821</v>
         <stp/>
         <stp>BDP|12384116645427329600</stp>
         <tr r="D436" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2330030029</v>
+        <v>#N/A Requesting Data...3378428722</v>
         <stp/>
         <stp>BDP|16598251105027212500</stp>
         <tr r="D228" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...710102165</v>
+        <v>#N/A Requesting Data...3097024880</v>
         <stp/>
         <stp>BDP|15327473017427272160</stp>
         <tr r="D392" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4252237554</v>
+        <v>#N/A Requesting Data...1245479992</v>
         <stp/>
         <stp>BDP|10638185858702371020</stp>
         <tr r="D31" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1099133070</v>
+        <v>#N/A Requesting Data...2487849256</v>
         <stp/>
         <stp>BDP|16109719660818306952</stp>
         <tr r="D564" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4149608855</v>
+        <v>#N/A Requesting Data...4031945133</v>
         <stp/>
         <stp>BDP|13940619371823197614</stp>
         <tr r="D382" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1039373945</v>
+        <v>#N/A Requesting Data...1015623622</v>
         <stp/>
         <stp>BDP|16679837039722107844</stp>
         <tr r="D543" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...689088433</v>
+        <v>#N/A Requesting Data...2671010086</v>
         <stp/>
         <stp>BDP|10226623571365007383</stp>
         <tr r="D70" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...422177539</v>
+        <v>#N/A Requesting Data...4190556998</v>
         <stp/>
         <stp>BDP|15788327046200913501</stp>
         <tr r="D103" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3159983153</v>
+        <v>#N/A Requesting Data...1589775122</v>
         <stp/>
         <stp>BDP|11645472449562339411</stp>
         <tr r="D316" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1558614597</v>
+        <v>#N/A Requesting Data...900668918</v>
         <stp/>
         <stp>BDP|12176047634383479586</stp>
         <tr r="D102" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4198750660</v>
+        <v>#N/A Requesting Data...2915725734</v>
         <stp/>
         <stp>BDP|12965772700751131321</stp>
         <tr r="D11" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3452843168</v>
+        <v>#N/A Requesting Data...2937176709</v>
         <stp/>
         <stp>BDP|14492683184025366843</stp>
         <tr r="D509" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2781986050</v>
+        <v>#N/A Requesting Data...4200950084</v>
         <stp/>
         <stp>BDP|13621156919710112459</stp>
         <tr r="D505" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3749805166</v>
+        <v>#N/A Requesting Data...3474404418</v>
         <stp/>
         <stp>BDP|10612094947086786516</stp>
         <tr r="D476" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2678358467</v>
+        <v>#N/A Requesting Data...1707053683</v>
         <stp/>
         <stp>BDP|11766851994124171367</stp>
         <tr r="D206" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...595220175</v>
+        <v>#N/A Requesting Data...1440420747</v>
         <stp/>
         <stp>BDP|15751556461691453064</stp>
         <tr r="D56" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3398682941</v>
+        <v>#N/A Requesting Data...2979546865</v>
         <stp/>
         <stp>BDP|17430058153027313218</stp>
         <tr r="D199" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3144958925</v>
+        <v>#N/A Requesting Data...1211399960</v>
         <stp/>
         <stp>BDP|13410803446581281909</stp>
         <tr r="D303" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2003285450</v>
+        <v>#N/A Requesting Data...3577544458</v>
         <stp/>
         <stp>BDP|14214024771250412450</stp>
         <tr r="D69" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1831905895</v>
+        <v>#N/A Requesting Data...2763683314</v>
         <stp/>
         <stp>BDP|17567428413495056073</stp>
         <tr r="D89" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...901497552</v>
+        <v>#N/A Requesting Data...678929450</v>
         <stp/>
         <stp>BDP|10210200937601583733</stp>
         <tr r="D180" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3603433326</v>
+        <v>#N/A Requesting Data...2477492705</v>
         <stp/>
         <stp>BDP|10293556900733412178</stp>
         <tr r="D97" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2109552129</v>
+        <v>#N/A Requesting Data...2766062882</v>
         <stp/>
         <stp>BDP|11695358075697338523</stp>
         <tr r="D294" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...425546494</v>
+        <v>#N/A Requesting Data...1060796866</v>
         <stp/>
         <stp>BDP|14006055271880900757</stp>
         <tr r="D479" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...385285582</v>
+        <v>#N/A Requesting Data...3081346593</v>
         <stp/>
         <stp>BDP|12910810023405018933</stp>
         <tr r="D502" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3896852277</v>
+        <v>#N/A Requesting Data...1238294181</v>
         <stp/>
         <stp>BDP|11048718063874713084</stp>
         <tr r="D295" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...323931917</v>
+        <v>#N/A Requesting Data...3596865633</v>
         <stp/>
         <stp>BDP|13780959142678828255</stp>
         <tr r="D458" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3053379426</v>
+        <v>#N/A Requesting Data...1798670426</v>
         <stp/>
         <stp>BDP|14982632061692128279</stp>
         <tr r="D430" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1503261492</v>
+        <v>#N/A Requesting Data...1244796653</v>
         <stp/>
         <stp>BDP|17489095340364755366</stp>
         <tr r="D388" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4014760553</v>
+        <v>#N/A Requesting Data...4004411471</v>
         <stp/>
         <stp>BDP|14154434549619749934</stp>
         <tr r="D461" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2541633026</v>
+        <v>#N/A Requesting Data...1325948472</v>
         <stp/>
         <stp>BDP|16171649309956210209</stp>
         <tr r="D200" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2043599533</v>
+        <v>#N/A Requesting Data...847095700</v>
         <stp/>
         <stp>BDP|17738622573885864709</stp>
         <tr r="D529" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3635551125</v>
+        <v>#N/A Requesting Data...3695899806</v>
         <stp/>
         <stp>BDP|16357139949901679616</stp>
         <tr r="D551" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2644590438</v>
+        <v>#N/A Requesting Data...1909523206</v>
         <stp/>
         <stp>BDP|11975136771094310792</stp>
         <tr r="D322" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1415783304</v>
+        <v>#N/A Requesting Data...2702790637</v>
         <stp/>
         <stp>BDP|10411824585493459779</stp>
         <tr r="D270" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1596676874</v>
+        <v>#N/A Requesting Data...1076481488</v>
         <stp/>
         <stp>BDP|15265204922544150514</stp>
         <tr r="D484" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1169501032</v>
+        <v>#N/A Requesting Data...1920746970</v>
         <stp/>
         <stp>BDP|16769656722202312408</stp>
         <tr r="D399" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3899294521</v>
+        <v>#N/A Requesting Data...1131084225</v>
         <stp/>
         <stp>BDP|17611076792082454852</stp>
         <tr r="D363" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...979111890</v>
+        <v>#N/A Requesting Data...2767023515</v>
         <stp/>
         <stp>BDP|13134562330161259073</stp>
         <tr r="D585" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3337876541</v>
+        <v>#N/A Requesting Data...1320252438</v>
         <stp/>
         <stp>BDP|12871185857632217006</stp>
         <tr r="D155" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3089557033</v>
+        <v>#N/A Requesting Data...977851306</v>
         <stp/>
         <stp>BDP|16134536803102189546</stp>
         <tr r="D83" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3678916248</v>
+        <v>#N/A Requesting Data...2406642685</v>
         <stp/>
         <stp>BDP|14328250418885925632</stp>
         <tr r="D84" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3393266188</v>
+        <v>#N/A Requesting Data...2782994306</v>
         <stp/>
         <stp>BDP|14934686065876684669</stp>
         <tr r="D481" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...402536531</v>
+        <v>#N/A Requesting Data...3140288826</v>
         <stp/>
         <stp>BDP|17963550531373117687</stp>
         <tr r="D225" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2347429069</v>
+        <v>#N/A Requesting Data...3341629346</v>
         <stp/>
         <stp>BDP|16895936320721591899</stp>
         <tr r="D497" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2631250788</v>
+        <v>#N/A Requesting Data...3315591090</v>
         <stp/>
         <stp>BDP|16458841682844237679</stp>
         <tr r="D420" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1932906782</v>
+        <v>#N/A Requesting Data...3336907207</v>
         <stp/>
         <stp>BDP|14440303204491185270</stp>
         <tr r="D171" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3430213354</v>
+        <v>#N/A Requesting Data...1994864075</v>
         <stp/>
         <stp>BDP|14165715331463152764</stp>
         <tr r="D371" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3534967887</v>
+        <v>#N/A Requesting Data...3030342810</v>
         <stp/>
         <stp>BDP|15605708855175923735</stp>
         <tr r="D95" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2961808967</v>
+        <v>#N/A Requesting Data...3305773933</v>
         <stp/>
         <stp>BDP|14405119893020935975</stp>
         <tr r="D75" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3833427299</v>
+        <v>#N/A Requesting Data...817841257</v>
         <stp/>
         <stp>BDP|15767153234412924075</stp>
         <tr r="D177" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3557625591</v>
+        <v>#N/A Requesting Data...1077501316</v>
         <stp/>
         <stp>BDP|14059473339945099355</stp>
         <tr r="D580" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3783651859</v>
+        <v>#N/A Requesting Data...3274646679</v>
         <stp/>
         <stp>BDP|14264765733443828644</stp>
         <tr r="D9" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3558322165</v>
+        <v>#N/A Requesting Data...1239139707</v>
         <stp/>
         <stp>BDP|18273378097007086097</stp>
         <tr r="D302" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3846437850</v>
+        <v>#N/A Requesting Data...2221578533</v>
         <stp/>
         <stp>BDP|11895865234956147910</stp>
         <tr r="D379" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...794557367</v>
+        <v>#N/A Requesting Data...3667592806</v>
         <stp/>
         <stp>BDP|16982959482033162150</stp>
         <tr r="D421" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2850304246</v>
+        <v>#N/A Requesting Data...4227302081</v>
         <stp/>
         <stp>BDP|13586216918044734164</stp>
         <tr r="D80" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...689414842</v>
+        <v>#N/A Requesting Data...2745501060</v>
         <stp/>
         <stp>BDP|11217978724517557889</stp>
         <tr r="D466" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2868496420</v>
+        <v>#N/A Requesting Data...3730963919</v>
         <stp/>
         <stp>BDP|17018395540714763103</stp>
         <tr r="D589" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2900964019</v>
+        <v>#N/A Requesting Data...2778378838</v>
         <stp/>
         <stp>BDP|11382653934608536966</stp>
         <tr r="D344" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1080954640</v>
+        <v>#N/A Requesting Data...1609280300</v>
         <stp/>
         <stp>BDP|15505903805289095019</stp>
         <tr r="D424" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1271744491</v>
+        <v>#N/A Requesting Data...3498617508</v>
         <stp/>
         <stp>BDP|16883807256079921772</stp>
         <tr r="D24" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4015709516</v>
+        <v>#N/A Requesting Data...3371273728</v>
         <stp/>
         <stp>BDP|14952619124202580797</stp>
         <tr r="D195" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...610736999</v>
+        <v>#N/A Requesting Data...3134419613</v>
         <stp/>
         <stp>BDP|14910103472521146697</stp>
         <tr r="D311" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1786388037</v>
+        <v>#N/A Requesting Data...3584844097</v>
         <stp/>
         <stp>BDP|11334666327558605816</stp>
         <tr r="D477" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...755132554</v>
+        <v>#N/A Requesting Data...3315812843</v>
         <stp/>
         <stp>BDP|13699391622210844735</stp>
         <tr r="D53" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...406030327</v>
+        <v>#N/A Requesting Data...2221664133</v>
         <stp/>
         <stp>BDP|14503831410191139918</stp>
         <tr r="D503" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2596004452</v>
+        <v>#N/A Requesting Data...960793976</v>
         <stp/>
         <stp>BDP|14315355472065754058</stp>
         <tr r="D117" s="1"/>
@@ -3577,1837 +3577,1837 @@
     </main>
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...3880112656</v>
+        <v>#N/A Requesting Data...3296685680</v>
         <stp/>
         <stp>BDP|7623050384811565284</stp>
         <tr r="D456" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4053480049</v>
+        <v>#N/A Requesting Data...4021542752</v>
         <stp/>
         <stp>BDP|1639870690614204895</stp>
         <tr r="D283" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2587734771</v>
+        <v>#N/A Requesting Data...3208293228</v>
         <stp/>
         <stp>BDP|7243076913818545285</stp>
         <tr r="D507" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...854780185</v>
+        <v>#N/A Requesting Data...3283943921</v>
         <stp/>
         <stp>BDP|8226930168399527275</stp>
         <tr r="D128" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3149967393</v>
+        <v>#N/A Requesting Data...3981870712</v>
         <stp/>
         <stp>BDP|9726871053711847932</stp>
         <tr r="D186" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4113116403</v>
+        <v>#N/A Requesting Data...3637380869</v>
         <stp/>
         <stp>BDP|9497836528218660747</stp>
         <tr r="D52" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2121272529</v>
+        <v>#N/A Requesting Data...2275816337</v>
         <stp/>
         <stp>BDP|8111275640784203693</stp>
         <tr r="D575" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1049560210</v>
+        <v>#N/A Requesting Data...1654881347</v>
         <stp/>
         <stp>BDP|9193067224492806592</stp>
         <tr r="D366" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3802932603</v>
+        <v>#N/A Requesting Data...1230235241</v>
         <stp/>
         <stp>BDP|6738941727803649205</stp>
         <tr r="D342" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...687279558</v>
+        <v>#N/A Requesting Data...3075395262</v>
         <stp/>
         <stp>BDP|2772095382833635584</stp>
         <tr r="D472" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2029653509</v>
+        <v>#N/A Requesting Data...2463987396</v>
         <stp/>
         <stp>BDP|9536108630005175278</stp>
         <tr r="D29" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3302642892</v>
+        <v>#N/A Requesting Data...2002253827</v>
         <stp/>
         <stp>BDP|6784772766698072363</stp>
         <tr r="D187" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4141561750</v>
+        <v>#N/A Requesting Data...3042189669</v>
         <stp/>
         <stp>BDP|9893747310534920752</stp>
         <tr r="D368" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1281868249</v>
+        <v>#N/A Requesting Data...793945743</v>
         <stp/>
         <stp>BDP|9816011918836325221</stp>
         <tr r="D219" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2145248304</v>
+        <v>#N/A Requesting Data...3205671035</v>
         <stp/>
         <stp>BDP|8933781651680340636</stp>
         <tr r="D189" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2290095309</v>
+        <v>#N/A Requesting Data...3568672794</v>
         <stp/>
         <stp>BDP|2493805631473219662</stp>
         <tr r="D215" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3258868643</v>
+        <v>#N/A Requesting Data...3069383865</v>
         <stp/>
         <stp>BDP|1924192329366049887</stp>
         <tr r="D332" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1467101788</v>
+        <v>#N/A Requesting Data...2997655992</v>
         <stp/>
         <stp>BDP|4599658466598383039</stp>
         <tr r="D197" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2199398476</v>
+        <v>#N/A Requesting Data...930464399</v>
         <stp/>
         <stp>BDP|4734802498351823809</stp>
         <tr r="D422" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2049309672</v>
+        <v>#N/A Requesting Data...3676481921</v>
         <stp/>
         <stp>BDP|8738485985869825152</stp>
         <tr r="D534" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4092068828</v>
+        <v>#N/A Requesting Data...2607575481</v>
         <stp/>
         <stp>BDP|2868991425637522243</stp>
         <tr r="D556" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2146590986</v>
+        <v>#N/A Requesting Data...2280435088</v>
         <stp/>
         <stp>BDP|4886320651247275828</stp>
         <tr r="D126" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...779807678</v>
+        <v>#N/A Requesting Data...2984814102</v>
         <stp/>
         <stp>BDP|6054904808547626501</stp>
         <tr r="D239" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1006756033</v>
+        <v>#N/A Requesting Data...2197754178</v>
         <stp/>
         <stp>BDP|4165772881303842502</stp>
         <tr r="D21" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2141039689</v>
+        <v>#N/A Requesting Data...3685585867</v>
         <stp/>
         <stp>BDP|6358533107418304681</stp>
         <tr r="D537" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2876591029</v>
+        <v>#N/A Requesting Data...4150954762</v>
         <stp/>
         <stp>BDP|1584911349124970593</stp>
         <tr r="D418" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...979626253</v>
+        <v>#N/A Requesting Data...3922664699</v>
         <stp/>
         <stp>BDP|6294497581632428536</stp>
         <tr r="D372" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4072717311</v>
+        <v>#N/A Requesting Data...2126010659</v>
         <stp/>
         <stp>BDP|7804752713578077434</stp>
         <tr r="D48" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3984297743</v>
+        <v>#N/A Requesting Data...1386086188</v>
         <stp/>
         <stp>BDP|8000248422975254092</stp>
         <tr r="D94" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1177280580</v>
+        <v>#N/A Requesting Data...4035043033</v>
         <stp/>
         <stp>BDP|9902293861928289809</stp>
         <tr r="D370" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3568878626</v>
+        <v>#N/A Requesting Data...2753358961</v>
         <stp/>
         <stp>BDP|6133403049878320388</stp>
         <tr r="D325" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2896204458</v>
+        <v>#N/A Requesting Data...3313727145</v>
         <stp/>
         <stp>BDP|9727535323223702031</stp>
         <tr r="D306" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1985188366</v>
+        <v>#N/A Requesting Data...3364032427</v>
         <stp/>
         <stp>BDP|6127197419049389227</stp>
         <tr r="D571" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2718986461</v>
+        <v>#N/A Requesting Data...2133878486</v>
         <stp/>
         <stp>BDP|6094821283188207353</stp>
         <tr r="D107" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3339468315</v>
+        <v>#N/A Requesting Data...3042017289</v>
         <stp/>
         <stp>BDP|6031175296491070275</stp>
         <tr r="D317" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1512164710</v>
+        <v>#N/A Requesting Data...2043892714</v>
         <stp/>
         <stp>BDP|8749193567017735587</stp>
         <tr r="D560" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2215969110</v>
+        <v>#N/A Requesting Data...1603174332</v>
         <stp/>
         <stp>BDP|9446715963652157715</stp>
         <tr r="D218" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3392028018</v>
+        <v>#N/A Requesting Data...1970332554</v>
         <stp/>
         <stp>BDP|2285355385367559306</stp>
         <tr r="D254" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...443291429</v>
+        <v>#N/A Requesting Data...3758361647</v>
         <stp/>
         <stp>BDP|3377919900382605532</stp>
         <tr r="D374" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1522194736</v>
+        <v>#N/A Requesting Data...1325796800</v>
         <stp/>
         <stp>BDP|7453522301018176725</stp>
         <tr r="D87" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...489016068</v>
+        <v>#N/A Requesting Data...2908917125</v>
         <stp/>
         <stp>BDP|1308349689585926227</stp>
         <tr r="D271" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1189442305</v>
+        <v>#N/A Requesting Data...3986639856</v>
         <stp/>
         <stp>BDP|7855343402469312377</stp>
         <tr r="D207" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1747392681</v>
+        <v>#N/A Requesting Data...838081323</v>
         <stp/>
         <stp>BDP|9583460284713835858</stp>
         <tr r="D407" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3295683233</v>
+        <v>#N/A Requesting Data...3786655847</v>
         <stp/>
         <stp>BDP|3089794467698124477</stp>
         <tr r="D46" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3948339601</v>
+        <v>#N/A Requesting Data...3410539047</v>
         <stp/>
         <stp>BDP|8394730019619504937</stp>
         <tr r="D132" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4063672542</v>
+        <v>#N/A Requesting Data...1090112222</v>
         <stp/>
         <stp>BDP|8883884209098016656</stp>
         <tr r="D76" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3703896591</v>
+        <v>#N/A Requesting Data...3725145901</v>
         <stp/>
         <stp>BDP|8122536761650498550</stp>
         <tr r="D536" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1195736950</v>
+        <v>#N/A Requesting Data...1018966633</v>
         <stp/>
         <stp>BDP|7453339047569124725</stp>
         <tr r="D150" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...805506840</v>
+        <v>#N/A Requesting Data...1864912935</v>
         <stp/>
         <stp>BDP|7577357505142764827</stp>
         <tr r="D233" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1741377503</v>
+        <v>#N/A Requesting Data...3702253881</v>
         <stp/>
         <stp>BDP|2331805259517323692</stp>
         <tr r="D434" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4072108209</v>
+        <v>#N/A Requesting Data...1575536805</v>
         <stp/>
         <stp>BDP|8552162123980605570</stp>
         <tr r="D307" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1944499241</v>
+        <v>#N/A Requesting Data...1773411460</v>
         <stp/>
         <stp>BDP|5836558290245842234</stp>
         <tr r="D469" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2621738032</v>
+        <v>#N/A Requesting Data...2663856600</v>
         <stp/>
         <stp>BDP|2306149199512209683</stp>
         <tr r="D68" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1545361094</v>
+        <v>#N/A Requesting Data...967683619</v>
         <stp/>
         <stp>BDP|9269908147763082911</stp>
         <tr r="D510" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4137877795</v>
+        <v>#N/A Requesting Data...1188711397</v>
         <stp/>
         <stp>BDP|3232196262018907246</stp>
         <tr r="D318" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1218850593</v>
+        <v>#N/A Requesting Data...4134109891</v>
         <stp/>
         <stp>BDP|4955062808609747343</stp>
         <tr r="D246" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...753014575</v>
+        <v>#N/A Requesting Data...2290018289</v>
         <stp/>
         <stp>BDP|1722688294446534746</stp>
         <tr r="D298" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4239478174</v>
+        <v>#N/A Requesting Data...1079946963</v>
         <stp/>
         <stp>BDP|1323672309431259951</stp>
         <tr r="D248" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2933853505</v>
+        <v>#N/A Requesting Data...1230844218</v>
         <stp/>
         <stp>BDP|9788636929946362445</stp>
         <tr r="D51" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...848255882</v>
+        <v>#N/A Requesting Data...1711310645</v>
         <stp/>
         <stp>BDP|1530258288214479079</stp>
         <tr r="D346" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2352822411</v>
+        <v>#N/A Requesting Data...830999846</v>
         <stp/>
         <stp>BDP|9358636045517981357</stp>
         <tr r="D86" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2947902929</v>
+        <v>#N/A Requesting Data...2744925123</v>
         <stp/>
         <stp>BDP|3017892803863663751</stp>
         <tr r="D170" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...502028054</v>
+        <v>#N/A Requesting Data...3660037753</v>
         <stp/>
         <stp>BDP|4287398081092613222</stp>
         <tr r="D304" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2248678506</v>
+        <v>#N/A Requesting Data...3450518737</v>
         <stp/>
         <stp>BDP|9702212431560385792</stp>
         <tr r="D156" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...785910650</v>
+        <v>#N/A Requesting Data...3900465343</v>
         <stp/>
         <stp>BDP|2475470421272895971</stp>
         <tr r="D3" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3970076943</v>
+        <v>#N/A Requesting Data...1212859282</v>
         <stp/>
         <stp>BDP|2985262289595087247</stp>
         <tr r="D426" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...582825619</v>
+        <v>#N/A Requesting Data...1917770826</v>
         <stp/>
         <stp>BDP|8092118407590216646</stp>
         <tr r="D289" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2834888025</v>
+        <v>#N/A Requesting Data...1968090790</v>
         <stp/>
         <stp>BDP|5882374297019809911</stp>
         <tr r="D356" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2706999673</v>
+        <v>#N/A Requesting Data...4236155435</v>
         <stp/>
         <stp>BDP|3099892622757851151</stp>
         <tr r="D326" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3401382822</v>
+        <v>#N/A Requesting Data...2048687885</v>
         <stp/>
         <stp>BDP|9196098449071202363</stp>
         <tr r="D446" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1145786794</v>
+        <v>#N/A Requesting Data...1460690353</v>
         <stp/>
         <stp>BDP|4940011471029696259</stp>
         <tr r="D278" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2589594861</v>
+        <v>#N/A Requesting Data...2952023395</v>
         <stp/>
         <stp>BDP|8925989482633184281</stp>
         <tr r="D138" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1528736513</v>
+        <v>#N/A Requesting Data...2497964846</v>
         <stp/>
         <stp>BDP|4326595937163076966</stp>
         <tr r="D229" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2531710565</v>
+        <v>#N/A Requesting Data...2926074831</v>
         <stp/>
         <stp>BDP|8310852319881722801</stp>
         <tr r="D93" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1138640716</v>
+        <v>#N/A Requesting Data...1247821866</v>
         <stp/>
         <stp>BDP|8647180025583570068</stp>
         <tr r="D154" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3712496331</v>
+        <v>#N/A Requesting Data...1985989002</v>
         <stp/>
         <stp>BDP|9591862357728023480</stp>
         <tr r="D231" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1244876417</v>
+        <v>#N/A Requesting Data...4184067377</v>
         <stp/>
         <stp>BDP|2376736184992986702</stp>
         <tr r="D148" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1421809347</v>
+        <v>#N/A Requesting Data...2207500856</v>
         <stp/>
         <stp>BDP|4397980744471996074</stp>
         <tr r="D545" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2986182689</v>
+        <v>#N/A Requesting Data...1093219911</v>
         <stp/>
         <stp>BDP|8097652200812551411</stp>
         <tr r="D587" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2184460966</v>
+        <v>#N/A Requesting Data...3852322094</v>
         <stp/>
         <stp>BDP|4745617288346912467</stp>
         <tr r="D409" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3403601578</v>
+        <v>#N/A Requesting Data...3610820655</v>
         <stp/>
         <stp>BDP|2023918701830752311</stp>
         <tr r="D574" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1616270096</v>
+        <v>#N/A Requesting Data...1540978054</v>
         <stp/>
         <stp>BDP|8569623810236292112</stp>
         <tr r="D470" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1601285029</v>
+        <v>#N/A Requesting Data...2873215783</v>
         <stp/>
         <stp>BDP|3551133417799288277</stp>
         <tr r="D131" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...832066921</v>
+        <v>#N/A Requesting Data...2723806333</v>
         <stp/>
         <stp>BDP|1450583398923450654</stp>
         <tr r="D527" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2573371139</v>
+        <v>#N/A Requesting Data...2632304761</v>
         <stp/>
         <stp>BDP|8236278446435877201</stp>
         <tr r="D249" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...694172801</v>
+        <v>#N/A Requesting Data...2058693986</v>
         <stp/>
         <stp>BDP|9033149665613312496</stp>
         <tr r="D79" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1484132860</v>
+        <v>#N/A Requesting Data...3595616794</v>
         <stp/>
         <stp>BDP|4123587993102589346</stp>
         <tr r="D165" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1418106224</v>
+        <v>#N/A Requesting Data...3734962370</v>
         <stp/>
         <stp>BDP|6846058092115500312</stp>
         <tr r="D125" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2576573571</v>
+        <v>#N/A Requesting Data...1931874115</v>
         <stp/>
         <stp>BDP|3091327299045487544</stp>
         <tr r="D250" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2172596662</v>
+        <v>#N/A Requesting Data...4265891649</v>
         <stp/>
         <stp>BDP|8481692292877637901</stp>
         <tr r="D244" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1700219223</v>
+        <v>#N/A Requesting Data...3939912202</v>
         <stp/>
         <stp>BDP|8136255956607343184</stp>
         <tr r="D435" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...501666665</v>
+        <v>#N/A Requesting Data...4092428901</v>
         <stp/>
         <stp>BDP|9440620749352114075</stp>
         <tr r="D12" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...950017092</v>
+        <v>#N/A Requesting Data...4223728671</v>
         <stp/>
         <stp>BDP|7925481559807704869</stp>
         <tr r="D284" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3929283567</v>
+        <v>#N/A Requesting Data...2420868564</v>
         <stp/>
         <stp>BDP|3801820060333595716</stp>
         <tr r="D531" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2983697339</v>
+        <v>#N/A Requesting Data...3900279520</v>
         <stp/>
         <stp>BDP|7034930101581194604</stp>
         <tr r="D364" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3250439744</v>
+        <v>#N/A Requesting Data...1166639177</v>
         <stp/>
         <stp>BDP|7218848724570672446</stp>
         <tr r="D77" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1400497971</v>
+        <v>#N/A Requesting Data...3851489549</v>
         <stp/>
         <stp>BDP|2631777211879045408</stp>
         <tr r="D423" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1593782120</v>
+        <v>#N/A Requesting Data...1724381538</v>
         <stp/>
         <stp>BDP|6289685288420213178</stp>
         <tr r="D427" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...612442765</v>
+        <v>#N/A Requesting Data...1138399288</v>
         <stp/>
         <stp>BDP|4896326759068319347</stp>
         <tr r="D301" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...814942414</v>
+        <v>#N/A Requesting Data...1167626268</v>
         <stp/>
         <stp>BDP|6668119832509858494</stp>
         <tr r="D377" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1699893522</v>
+        <v>#N/A Requesting Data...1642579185</v>
         <stp/>
         <stp>BDP|3227235482723725318</stp>
         <tr r="D268" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1998707093</v>
+        <v>#N/A Requesting Data...3821870349</v>
         <stp/>
         <stp>BDP|9529448341521306165</stp>
         <tr r="D519" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2042089078</v>
+        <v>#N/A Requesting Data...3337256304</v>
         <stp/>
         <stp>BDP|1815156912700842820</stp>
         <tr r="D149" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...759903016</v>
+        <v>#N/A Requesting Data...4090035172</v>
         <stp/>
         <stp>BDP|9918332901022829283</stp>
         <tr r="D257" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2476612835</v>
+        <v>#N/A Requesting Data...3095186769</v>
         <stp/>
         <stp>BDP|8570410628420469403</stp>
         <tr r="D308" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4187827968</v>
+        <v>#N/A Requesting Data...2632678651</v>
         <stp/>
         <stp>BDP|5366710529858496212</stp>
         <tr r="D101" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3681514723</v>
+        <v>#N/A Requesting Data...1723181004</v>
         <stp/>
         <stp>BDP|5295290977009503366</stp>
         <tr r="D137" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...873291622</v>
+        <v>#N/A Requesting Data...3976882446</v>
         <stp/>
         <stp>BDP|1607716463123808934</stp>
         <tr r="D121" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1882164584</v>
+        <v>#N/A Requesting Data...2678957054</v>
         <stp/>
         <stp>BDP|9904390111005448478</stp>
         <tr r="D276" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3390739151</v>
+        <v>#N/A Requesting Data...1840585982</v>
         <stp/>
         <stp>BDP|1075940526831975184</stp>
         <tr r="D106" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...565440312</v>
+        <v>#N/A Requesting Data...3593415374</v>
         <stp/>
         <stp>BDP|3451332904323552978</stp>
         <tr r="D489" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2419035375</v>
+        <v>#N/A Requesting Data...2949377637</v>
         <stp/>
         <stp>BDP|5584379463772680863</stp>
         <tr r="D333" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1966220366</v>
+        <v>#N/A Requesting Data...2037116017</v>
         <stp/>
         <stp>BDP|2125938060654101321</stp>
         <tr r="D109" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1053418086</v>
+        <v>#N/A Requesting Data...2705092805</v>
         <stp/>
         <stp>BDP|4870943729911367476</stp>
         <tr r="D273" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2468655571</v>
+        <v>#N/A Requesting Data...3022670648</v>
         <stp/>
         <stp>BDP|9377653440733839289</stp>
         <tr r="D578" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3869010882</v>
+        <v>#N/A Requesting Data...2712502565</v>
         <stp/>
         <stp>BDP|9892995884015450771</stp>
         <tr r="D100" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2068118529</v>
+        <v>#N/A Requesting Data...3834310158</v>
         <stp/>
         <stp>BDP|3034334267899211503</stp>
         <tr r="D54" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1914077473</v>
+        <v>#N/A Requesting Data...3737113211</v>
         <stp/>
         <stp>BDP|7104452733023208929</stp>
         <tr r="D425" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2235869204</v>
+        <v>#N/A Requesting Data...1991909731</v>
         <stp/>
         <stp>BDP|6179752583840472360</stp>
         <tr r="D460" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2685222774</v>
+        <v>#N/A Requesting Data...3143920319</v>
         <stp/>
         <stp>BDP|1509076953006623821</stp>
         <tr r="D286" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3934802112</v>
+        <v>#N/A Requesting Data...2038652197</v>
         <stp/>
         <stp>BDP|9554476425145314015</stp>
         <tr r="D205" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3598070876</v>
+        <v>#N/A Requesting Data...1191264248</v>
         <stp/>
         <stp>BDP|6239748591173887059</stp>
         <tr r="D429" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3670233676</v>
+        <v>#N/A Requesting Data...4270118380</v>
         <stp/>
         <stp>BDP|1820733751689406148</stp>
         <tr r="D64" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4260435893</v>
+        <v>#N/A Requesting Data...3586446536</v>
         <stp/>
         <stp>BDP|2909876244543694673</stp>
         <tr r="D38" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3950117137</v>
+        <v>#N/A Requesting Data...989648064</v>
         <stp/>
         <stp>BDP|7505840236691418688</stp>
         <tr r="D313" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1342326862</v>
+        <v>#N/A Requesting Data...1693908010</v>
         <stp/>
         <stp>BDP|9248413818921784640</stp>
         <tr r="D576" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1015488506</v>
+        <v>#N/A Requesting Data...3291487537</v>
         <stp/>
         <stp>BDP|3067690985453535517</stp>
         <tr r="D398" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3560695876</v>
+        <v>#N/A Requesting Data...2025875000</v>
         <stp/>
         <stp>BDP|7769694405108217205</stp>
         <tr r="D329" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2958096663</v>
+        <v>#N/A Requesting Data...2622911274</v>
         <stp/>
         <stp>BDP|9359988577525473968</stp>
         <tr r="D297" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3015279951</v>
+        <v>#N/A Requesting Data...1231433015</v>
         <stp/>
         <stp>BDP|5395749799948894898</stp>
         <tr r="D443" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4098982908</v>
+        <v>#N/A Requesting Data...2124496675</v>
         <stp/>
         <stp>BDP|5133580335141437979</stp>
         <tr r="D193" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1417380268</v>
+        <v>#N/A Requesting Data...2444989873</v>
         <stp/>
         <stp>BDP|3937023403621314942</stp>
         <tr r="D221" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2190903854</v>
+        <v>#N/A Requesting Data...2079043238</v>
         <stp/>
         <stp>BDP|9936218804240792047</stp>
         <tr r="D264" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4236175230</v>
+        <v>#N/A Requesting Data...3429681842</v>
         <stp/>
         <stp>BDP|6683723787496846473</stp>
         <tr r="D10" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1160639076</v>
+        <v>#N/A Requesting Data...3841318911</v>
         <stp/>
         <stp>BDP|6165591596490232106</stp>
         <tr r="D58" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3759809764</v>
+        <v>#N/A Requesting Data...3275674310</v>
         <stp/>
         <stp>BDP|8617076344793842407</stp>
         <tr r="D280" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...784992265</v>
+        <v>#N/A Requesting Data...2676692604</v>
         <stp/>
         <stp>BDP|1804538441912435934</stp>
         <tr r="D25" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1589121127</v>
+        <v>#N/A Requesting Data...956165811</v>
         <stp/>
         <stp>BDP|2266425173972059816</stp>
         <tr r="D550" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3584870508</v>
+        <v>#N/A Requesting Data...2393260884</v>
         <stp/>
         <stp>BDP|7759220196935193217</stp>
         <tr r="D566" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3059400982</v>
+        <v>#N/A Requesting Data...2395436718</v>
         <stp/>
         <stp>BDP|9235165796339361326</stp>
         <tr r="D90" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3045060016</v>
+        <v>#N/A Requesting Data...1795550842</v>
         <stp/>
         <stp>BDP|1179954875723744756</stp>
         <tr r="D60" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...931963720</v>
+        <v>#N/A Requesting Data...2131801825</v>
         <stp/>
         <stp>BDP|8410475836822559607</stp>
         <tr r="D8" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3407370419</v>
+        <v>#N/A Requesting Data...3553207637</v>
         <stp/>
         <stp>BDP|2224215676234399877</stp>
         <tr r="D15" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1607276552</v>
+        <v>#N/A Requesting Data...1650003533</v>
         <stp/>
         <stp>BDP|4523336092233717620</stp>
         <tr r="D431" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...687488295</v>
+        <v>#N/A Requesting Data...3382542820</v>
         <stp/>
         <stp>BDP|1296179121871245805</stp>
         <tr r="D300" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...751742246</v>
+        <v>#N/A Requesting Data...4237591577</v>
         <stp/>
         <stp>BDP|3661654014668954788</stp>
         <tr r="D50" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3413556263</v>
+        <v>#N/A Requesting Data...2940415377</v>
         <stp/>
         <stp>BDP|9924052402727859504</stp>
         <tr r="D577" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3077124700</v>
+        <v>#N/A Requesting Data...1962552863</v>
         <stp/>
         <stp>BDP|8698180476532918744</stp>
         <tr r="D397" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1035934771</v>
+        <v>#N/A Requesting Data...1699493041</v>
         <stp/>
         <stp>BDP|7938038971357920380</stp>
         <tr r="D416" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...631140753</v>
+        <v>#N/A Requesting Data...3245846384</v>
         <stp/>
         <stp>BDP|5245281727411393061</stp>
         <tr r="D514" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3313593235</v>
+        <v>#N/A Requesting Data...3207341050</v>
         <stp/>
         <stp>BDP|1662580733301037226</stp>
         <tr r="D530" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1617775861</v>
+        <v>#N/A Requesting Data...3457915547</v>
         <stp/>
         <stp>BDP|7949109588613523941</stp>
         <tr r="D40" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2096885954</v>
+        <v>#N/A Requesting Data...3767624189</v>
         <stp/>
         <stp>BDP|7005215072217282174</stp>
         <tr r="D402" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2985704043</v>
+        <v>#N/A Requesting Data...2380587708</v>
         <stp/>
         <stp>BDP|7166920933601970908</stp>
         <tr r="D16" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4156020631</v>
+        <v>#N/A Requesting Data...1544934903</v>
         <stp/>
         <stp>BDP|3475908282603960415</stp>
         <tr r="D260" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1944664524</v>
+        <v>#N/A Requesting Data...4241723235</v>
         <stp/>
         <stp>BDP|5979420807602581651</stp>
         <tr r="D85" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2863017769</v>
+        <v>#N/A Requesting Data...1351198441</v>
         <stp/>
         <stp>BDP|5037422791715941867</stp>
         <tr r="D328" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3588622420</v>
+        <v>#N/A Requesting Data...1220156922</v>
         <stp/>
         <stp>BDP|5116413237123352498</stp>
         <tr r="D105" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...665216368</v>
+        <v>#N/A Requesting Data...4089185812</v>
         <stp/>
         <stp>BDP|9059260025225871998</stp>
         <tr r="D452" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3031781068</v>
+        <v>#N/A Requesting Data...1651459801</v>
         <stp/>
         <stp>BDP|1465345185619771632</stp>
         <tr r="D312" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4191856897</v>
+        <v>#N/A Requesting Data...2848856748</v>
         <stp/>
         <stp>BDP|7676464898769936601</stp>
         <tr r="D43" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3892906057</v>
+        <v>#N/A Requesting Data...1954202098</v>
         <stp/>
         <stp>BDP|3763114208884910301</stp>
         <tr r="D136" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3102978958</v>
+        <v>#N/A Requesting Data...1397682633</v>
         <stp/>
         <stp>BDP|8072681399763360154</stp>
         <tr r="D362" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2163098933</v>
+        <v>#N/A Requesting Data...2996790736</v>
         <stp/>
         <stp>BDP|3098417321774331448</stp>
         <tr r="D23" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...667112239</v>
+        <v>#N/A Requesting Data...4134331172</v>
         <stp/>
         <stp>BDP|7909255723500064281</stp>
         <tr r="D508" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1041005450</v>
+        <v>#N/A Requesting Data...2435684329</v>
         <stp/>
         <stp>BDP|2293378301535568153</stp>
         <tr r="D190" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1816357029</v>
+        <v>#N/A Requesting Data...2782476337</v>
         <stp/>
         <stp>BDP|2988184231824436105</stp>
         <tr r="D243" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1872205487</v>
+        <v>#N/A Requesting Data...1636910996</v>
         <stp/>
         <stp>BDP|3643798898531358908</stp>
         <tr r="D7" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1117485086</v>
+        <v>#N/A Requesting Data...1841036264</v>
         <stp/>
         <stp>BDP|9924585886009360805</stp>
         <tr r="D104" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3648889434</v>
+        <v>#N/A Requesting Data...1219150388</v>
         <stp/>
         <stp>BDP|8712628990813229129</stp>
         <tr r="D127" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2905798601</v>
+        <v>#N/A Requesting Data...3710910985</v>
         <stp/>
         <stp>BDP|8505754588400618169</stp>
         <tr r="D134" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3584044661</v>
+        <v>#N/A Requesting Data...1551540978</v>
         <stp/>
         <stp>BDP|7897752427741522573</stp>
         <tr r="D62" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2608529744</v>
+        <v>#N/A Requesting Data...999265107</v>
         <stp/>
         <stp>BDP|5152732906727402381</stp>
         <tr r="D213" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3203219732</v>
+        <v>#N/A Requesting Data...4294892412</v>
         <stp/>
         <stp>BDP|8591675065389753788</stp>
         <tr r="D122" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1967821122</v>
+        <v>#N/A Requesting Data...3575483158</v>
         <stp/>
         <stp>BDP|7862024903508011905</stp>
         <tr r="D37" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3883016931</v>
+        <v>#N/A Requesting Data...3597725618</v>
         <stp/>
         <stp>BDP|5373321633363852032</stp>
         <tr r="D230" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...662934910</v>
+        <v>#N/A Requesting Data...2315894149</v>
         <stp/>
         <stp>BDP|1867912855733271817</stp>
         <tr r="D266" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3297762333</v>
+        <v>#N/A Requesting Data...2951655001</v>
         <stp/>
         <stp>BDP|1889368929935854321</stp>
         <tr r="D487" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2402561636</v>
+        <v>#N/A Requesting Data...2822139852</v>
         <stp/>
         <stp>BDP|6028636575459971821</stp>
         <tr r="D133" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3535615449</v>
+        <v>#N/A Requesting Data...4211181953</v>
         <stp/>
         <stp>BDP|7722671022665348033</stp>
         <tr r="D474" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3432407660</v>
+        <v>#N/A Requesting Data...2711380902</v>
         <stp/>
         <stp>BDP|4660911983747217447</stp>
         <tr r="D352" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3421361093</v>
+        <v>#N/A Requesting Data...2267548552</v>
         <stp/>
         <stp>BDP|2499220431597090247</stp>
         <tr r="D354" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4050556580</v>
+        <v>#N/A Requesting Data...1605652927</v>
         <stp/>
         <stp>BDP|1762090205394266398</stp>
         <tr r="D118" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3089589585</v>
+        <v>#N/A Requesting Data...1395668780</v>
         <stp/>
         <stp>BDP|6288849757665878890</stp>
         <tr r="D299" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4191701434</v>
+        <v>#N/A Requesting Data...2586131065</v>
         <stp/>
         <stp>BDP|4578725706274497145</stp>
         <tr r="D78" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...897473476</v>
+        <v>#N/A Requesting Data...1461770477</v>
         <stp/>
         <stp>BDP|8563434988913791184</stp>
         <tr r="D115" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...845450054</v>
+        <v>#N/A Requesting Data...1245272933</v>
         <stp/>
         <stp>BDP|2713161853128675832</stp>
         <tr r="D438" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2614711181</v>
+        <v>#N/A Requesting Data...2787300224</v>
         <stp/>
         <stp>BDP|5375150814376172547</stp>
         <tr r="D183" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4277590676</v>
+        <v>#N/A Requesting Data...1878326681</v>
         <stp/>
         <stp>BDP|8361373044860119957</stp>
         <tr r="D91" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2054253076</v>
+        <v>#N/A Requesting Data...2501843226</v>
         <stp/>
         <stp>BDP|8534560576518547457</stp>
         <tr r="D194" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2988315976</v>
+        <v>#N/A Requesting Data...2847373490</v>
         <stp/>
         <stp>BDP|5189930998341893380</stp>
         <tr r="D202" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3079952282</v>
+        <v>#N/A Requesting Data...3459276265</v>
         <stp/>
         <stp>BDP|7287799954722430050</stp>
         <tr r="D500" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1914416685</v>
+        <v>#N/A Requesting Data...2195661327</v>
         <stp/>
         <stp>BDP|6238472035472816477</stp>
         <tr r="D237" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1723759702</v>
+        <v>#N/A Requesting Data...997378820</v>
         <stp/>
         <stp>BDP|2394784021459447921</stp>
         <tr r="D548" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1590769906</v>
+        <v>#N/A Requesting Data...3053669729</v>
         <stp/>
         <stp>BDP|3737498110312007328</stp>
         <tr r="D293" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2904085804</v>
+        <v>#N/A Requesting Data...2413476532</v>
         <stp/>
         <stp>BDP|3519651380778808240</stp>
         <tr r="D579" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1294171676</v>
+        <v>#N/A Requesting Data...1655375297</v>
         <stp/>
         <stp>BDP|2051744658246332136</stp>
         <tr r="D27" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3403547643</v>
+        <v>#N/A Requesting Data...2359306573</v>
         <stp/>
         <stp>BDP|4825030463322184747</stp>
         <tr r="D142" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3906570051</v>
+        <v>#N/A Requesting Data...2682669758</v>
         <stp/>
         <stp>BDP|7457262844856528015</stp>
         <tr r="D440" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2206881276</v>
+        <v>#N/A Requesting Data...2249273843</v>
         <stp/>
         <stp>BDP|4790028807567550453</stp>
         <tr r="D290" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1581222147</v>
+        <v>#N/A Requesting Data...3143723590</v>
         <stp/>
         <stp>BDP|7297790867386885764</stp>
         <tr r="D309" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3668985295</v>
+        <v>#N/A Requesting Data...1302110145</v>
         <stp/>
         <stp>BDP|1746752822412108129</stp>
         <tr r="D323" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2606570350</v>
+        <v>#N/A Requesting Data...2295593716</v>
         <stp/>
         <stp>BDP|1766375745043229240</stp>
         <tr r="D209" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2087683702</v>
+        <v>#N/A Requesting Data...2995079301</v>
         <stp/>
         <stp>BDP|4636711009917851376</stp>
         <tr r="D182" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...966697292</v>
+        <v>#N/A Requesting Data...2334584762</v>
         <stp/>
         <stp>BDP|8749935877251718052</stp>
         <tr r="D573" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...787634570</v>
+        <v>#N/A Requesting Data...1065391104</v>
         <stp/>
         <stp>BDP|8869233701588305582</stp>
         <tr r="D341" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3840225029</v>
+        <v>#N/A Requesting Data...2666103931</v>
         <stp/>
         <stp>BDP|7738528431062446460</stp>
         <tr r="D358" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3587227730</v>
+        <v>#N/A Requesting Data...1071198960</v>
         <stp/>
         <stp>BDP|1490451255536556166</stp>
         <tr r="D13" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2185238249</v>
+        <v>#N/A Requesting Data...2602347015</v>
         <stp/>
         <stp>BDP|4148629829775886254</stp>
         <tr r="D20" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1103068399</v>
+        <v>#N/A Requesting Data...1112604268</v>
         <stp/>
         <stp>BDP|5411126655507739108</stp>
         <tr r="D542" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1925067104</v>
+        <v>#N/A Requesting Data...3386910388</v>
         <stp/>
         <stp>BDP|3927876368834974974</stp>
         <tr r="D557" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3128414779</v>
+        <v>#N/A Requesting Data...4013747959</v>
         <stp/>
         <stp>BDP|7743598363670647451</stp>
         <tr r="D98" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3966240521</v>
+        <v>#N/A Requesting Data...2276395300</v>
         <stp/>
         <stp>BDP|7020272731156842016</stp>
         <tr r="D339" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2443782759</v>
+        <v>#N/A Requesting Data...3350741572</v>
         <stp/>
         <stp>BDP|7456297801813635661</stp>
         <tr r="D375" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2666380769</v>
+        <v>#N/A Requesting Data...3082566103</v>
         <stp/>
         <stp>BDP|5762374174869363840</stp>
         <tr r="D417" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2812722314</v>
+        <v>#N/A Requesting Data...3003014533</v>
         <stp/>
         <stp>BDP|3393157485503720975</stp>
         <tr r="D383" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1436029323</v>
+        <v>#N/A Requesting Data...1038894318</v>
         <stp/>
         <stp>BDP|5232840873708276242</stp>
         <tr r="D336" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3346441655</v>
+        <v>#N/A Requesting Data...3668810489</v>
         <stp/>
         <stp>BDP|3612173966712778635</stp>
         <tr r="D192" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2020243209</v>
+        <v>#N/A Requesting Data...3648413294</v>
         <stp/>
         <stp>BDP|3733447231434298019</stp>
         <tr r="D279" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...729163956</v>
+        <v>#N/A Requesting Data...3789945782</v>
         <stp/>
         <stp>BDP|7339243242099211862</stp>
         <tr r="D159" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3514600327</v>
+        <v>#N/A Requesting Data...4125820086</v>
         <stp/>
         <stp>BDP|2000625615164081168</stp>
         <tr r="D390" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...889985658</v>
+        <v>#N/A Requesting Data...1425770418</v>
         <stp/>
         <stp>BDP|9568729820545744946</stp>
         <tr r="D553" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4165466318</v>
+        <v>#N/A Requesting Data...3647379115</v>
         <stp/>
         <stp>BDP|7702250709236697386</stp>
         <tr r="D173" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2241506928</v>
+        <v>#N/A Requesting Data...3261121814</v>
         <stp/>
         <stp>BDP|3768594683288431739</stp>
         <tr r="D34" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2655010574</v>
+        <v>#N/A Requesting Data...2983807785</v>
         <stp/>
         <stp>BDP|3229626952947141698</stp>
         <tr r="D517" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3964515093</v>
+        <v>#N/A Requesting Data...1351097165</v>
         <stp/>
         <stp>BDP|1464757744162614196</stp>
         <tr r="D565" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3330753502</v>
+        <v>#N/A Requesting Data...3492084811</v>
         <stp/>
         <stp>BDP|5226776285259143295</stp>
         <tr r="D216" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...993491760</v>
+        <v>#N/A Requesting Data...3684598754</v>
         <stp/>
         <stp>BDP|1749196855906407265</stp>
         <tr r="D191" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3670564977</v>
+        <v>#N/A Requesting Data...3482138389</v>
         <stp/>
         <stp>BDP|6640473998318290254</stp>
         <tr r="D275" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2442092177</v>
+        <v>#N/A Requesting Data...3554175441</v>
         <stp/>
         <stp>BDP|7981643659250315583</stp>
         <tr r="D544" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2646466466</v>
+        <v>#N/A Requesting Data...2652020229</v>
         <stp/>
         <stp>BDP|1172786470216966627</stp>
         <tr r="D442" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1160013982</v>
+        <v>#N/A Requesting Data...3959119173</v>
         <stp/>
         <stp>BDP|4493965216098373541</stp>
         <tr r="D285" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4142882446</v>
+        <v>#N/A Requesting Data...2459475141</v>
         <stp/>
         <stp>BDP|8652953273535731244</stp>
         <tr r="D282" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1358378393</v>
+        <v>#N/A Requesting Data...3325900768</v>
         <stp/>
         <stp>BDP|6247261525487247021</stp>
         <tr r="D522" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2491175342</v>
+        <v>#N/A Requesting Data...2887300394</v>
         <stp/>
         <stp>BDP|8657366021000358849</stp>
         <tr r="D274" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3836847657</v>
+        <v>#N/A Requesting Data...1861038839</v>
         <stp/>
         <stp>BDP|6174475748970092785</stp>
         <tr r="D516" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3148666623</v>
+        <v>#N/A Requesting Data...2178527410</v>
         <stp/>
         <stp>BDP|3551612767713293152</stp>
         <tr r="D5" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2134362549</v>
+        <v>#N/A Requesting Data...1130351033</v>
         <stp/>
         <stp>BDP|3427098631898927908</stp>
         <tr r="D583" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2361940002</v>
+        <v>#N/A Requesting Data...4110624999</v>
         <stp/>
         <stp>BDP|7901869801916943829</stp>
         <tr r="D491" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4207073020</v>
+        <v>#N/A Requesting Data...1776935360</v>
         <stp/>
         <stp>BDP|1943553078210746265</stp>
         <tr r="D369" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2553403837</v>
+        <v>#N/A Requesting Data...4169650333</v>
         <stp/>
         <stp>BDP|4949023276263038251</stp>
         <tr r="D61" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...979959034</v>
+        <v>#N/A Requesting Data...1518752428</v>
         <stp/>
         <stp>BDP|4989584419047686578</stp>
         <tr r="D340" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3493254582</v>
+        <v>#N/A Requesting Data...2614875906</v>
         <stp/>
         <stp>BDP|6393796523609399841</stp>
         <tr r="D453" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3647508350</v>
+        <v>#N/A Requesting Data...1806178014</v>
         <stp/>
         <stp>BDP|4753245750303981269</stp>
         <tr r="D287" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3879657261</v>
+        <v>#N/A Requesting Data...1220358684</v>
         <stp/>
         <stp>BDP|2072281570842790722</stp>
         <tr r="D267" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1403687234</v>
+        <v>#N/A Requesting Data...2845979011</v>
         <stp/>
         <stp>BDP|3393122124422768007</stp>
         <tr r="D288" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3390948837</v>
+        <v>#N/A Requesting Data...2188160729</v>
         <stp/>
         <stp>BDP|4957503420636233786</stp>
         <tr r="D281" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1124984928</v>
+        <v>#N/A Requesting Data...2856510997</v>
         <stp/>
         <stp>BDP|3500293456512187488</stp>
         <tr r="D124" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3250238128</v>
+        <v>#N/A Requesting Data...3164322127</v>
         <stp/>
         <stp>BDP|8739978840685568234</stp>
         <tr r="D17" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3910226520</v>
+        <v>#N/A Requesting Data...3593678815</v>
         <stp/>
         <stp>BDP|4096269647590203048</stp>
         <tr r="D406" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2799432079</v>
+        <v>#N/A Requesting Data...2531825435</v>
         <stp/>
         <stp>BDP|7836319945986831400</stp>
         <tr r="D315" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1318964991</v>
+        <v>#N/A Requesting Data...1535101083</v>
         <stp/>
         <stp>BDP|6312760661944482144</stp>
         <tr r="D373" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2870596351</v>
+        <v>#N/A Requesting Data...3386900821</v>
         <stp/>
         <stp>BDP|8079996756815243264</stp>
         <tr r="D188" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3213002721</v>
+        <v>#N/A Requesting Data...1461543961</v>
         <stp/>
         <stp>BDP|2673628771994847449</stp>
         <tr r="D450" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...740152026</v>
+        <v>#N/A Requesting Data...1646719956</v>
         <stp/>
         <stp>BDP|2819857377356235874</stp>
         <tr r="D81" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2585490367</v>
+        <v>#N/A Requesting Data...3628392740</v>
         <stp/>
         <stp>BDP|6639434749407158216</stp>
         <tr r="D512" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3729502410</v>
+        <v>#N/A Requesting Data...3897174251</v>
         <stp/>
         <stp>BDP|6203570128133969183</stp>
         <tr r="D144" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...877840603</v>
+        <v>#N/A Requesting Data...3539170463</v>
         <stp/>
         <stp>BDP|1569887080373392132</stp>
         <tr r="D120" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1163852750</v>
+        <v>#N/A Requesting Data...1758117786</v>
         <stp/>
         <stp>BDP|9056453078160598956</stp>
         <tr r="D380" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1289132162</v>
+        <v>#N/A Requesting Data...1770643897</v>
         <stp/>
         <stp>BDP|6308584932105341675</stp>
         <tr r="D39" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4089549041</v>
+        <v>#N/A Requesting Data...2916379689</v>
         <stp/>
         <stp>BDP|7350319533614097031</stp>
         <tr r="D238" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1291181325</v>
+        <v>#N/A Requesting Data...2496293749</v>
         <stp/>
         <stp>BDP|6634135363243093163</stp>
         <tr r="D444" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2758235049</v>
+        <v>#N/A Requesting Data...2424439964</v>
         <stp/>
         <stp>BDP|8143426762301172816</stp>
         <tr r="D265" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3921847375</v>
+        <v>#N/A Requesting Data...3858009639</v>
         <stp/>
         <stp>BDP|3000832087751759158</stp>
         <tr r="D414" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3800444667</v>
+        <v>#N/A Requesting Data...3562658589</v>
         <stp/>
         <stp>BDP|3625079708654751491</stp>
         <tr r="D567" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4279177161</v>
+        <v>#N/A Requesting Data...3030248847</v>
         <stp/>
         <stp>BDP|1258866120959105126</stp>
         <tr r="D561" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2225938071</v>
+        <v>#N/A Requesting Data...1719710986</v>
         <stp/>
         <stp>BDP|1079611500885563136</stp>
         <tr r="D256" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2256691297</v>
+        <v>#N/A Requesting Data...2912090197</v>
         <stp/>
         <stp>BDP|3243968224278649323</stp>
         <tr r="D582" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4068147479</v>
+        <v>#N/A Requesting Data...4110030116</v>
         <stp/>
         <stp>BDP|3935741423492805726</stp>
         <tr r="D45" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1197731738</v>
+        <v>#N/A Requesting Data...1357230513</v>
         <stp/>
         <stp>BDP|8775461397464745249</stp>
         <tr r="D404" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3703080242</v>
+        <v>#N/A Requesting Data...1341420399</v>
         <stp/>
         <stp>BDP|4149497578023598709</stp>
         <tr r="D114" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3900570979</v>
+        <v>#N/A Requesting Data...3672966316</v>
         <stp/>
         <stp>BDP|2024817980394117554</stp>
         <tr r="D475" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...852153975</v>
+        <v>#N/A Requesting Data...3406452373</v>
         <stp/>
         <stp>BDP|7263781038469211956</stp>
         <tr r="D184" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2864844360</v>
+        <v>#N/A Requesting Data...3299854061</v>
         <stp/>
         <stp>BDP|6265204926545385028</stp>
         <tr r="D258" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4220723838</v>
+        <v>#N/A Requesting Data...2778230302</v>
         <stp/>
         <stp>BDP|48608902596895924</stp>
         <tr r="D55" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1601524304</v>
+        <v>#N/A Requesting Data...2037816702</v>
         <stp/>
         <stp>BDP|96904581314260211</stp>
         <tr r="D511" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4189207234</v>
+        <v>#N/A Requesting Data...1205088787</v>
         <stp/>
         <stp>BDP|48025756463849012</stp>
         <tr r="D324" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1184537239</v>
+        <v>#N/A Requesting Data...1672203474</v>
         <stp/>
         <stp>BDP|75451627768221885</stp>
         <tr r="D262" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1982176618</v>
+        <v>#N/A Requesting Data...2810015547</v>
         <stp/>
         <stp>BDP|602601916216927526</stp>
         <tr r="D347" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3050980960</v>
+        <v>#N/A Requesting Data...3977571640</v>
         <stp/>
         <stp>BDP|742317726280952669</stp>
         <tr r="D210" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3023276374</v>
+        <v>#N/A Requesting Data...1610903436</v>
         <stp/>
         <stp>BDP|536342472786416586</stp>
         <tr r="D405" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1990298883</v>
+        <v>#N/A Requesting Data...4167954404</v>
         <stp/>
         <stp>BDP|107192551852196126</stp>
         <tr r="D387" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2039061065</v>
+        <v>#N/A Requesting Data...1768539571</v>
         <stp/>
         <stp>BDP|363717428947256536</stp>
         <tr r="D459" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3299029742</v>
+        <v>#N/A Requesting Data...2958584285</v>
         <stp/>
         <stp>BDP|571806586507393013</stp>
         <tr r="D518" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3979257979</v>
+        <v>#N/A Requesting Data...1636225800</v>
         <stp/>
         <stp>BDP|724631544285136649</stp>
         <tr r="D269" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...928573109</v>
+        <v>#N/A Requesting Data...3434798856</v>
         <stp/>
         <stp>BDP|707009590311595971</stp>
         <tr r="D123" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3199025485</v>
+        <v>#N/A Requesting Data...4146775151</v>
         <stp/>
         <stp>BDP|358293908277290400</stp>
         <tr r="D178" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...841719024</v>
+        <v>#N/A Requesting Data...3899304072</v>
         <stp/>
         <stp>BDP|838178952767886270</stp>
         <tr r="D146" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2441624646</v>
+        <v>#N/A Requesting Data...1626802968</v>
         <stp/>
         <stp>BDP|265254163087537220</stp>
         <tr r="D44" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1914978759</v>
+        <v>#N/A Requesting Data...2954526401</v>
         <stp/>
         <stp>BDP|729321671512090681</stp>
         <tr r="D515" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2975396108</v>
+        <v>#N/A Requesting Data...1859674197</v>
         <stp/>
         <stp>BDP|159012462977714166</stp>
         <tr r="D359" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1400741420</v>
+        <v>#N/A Requesting Data...2493258506</v>
         <stp/>
         <stp>BDP|702676246109273800</stp>
         <tr r="D482" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2618225826</v>
+        <v>#N/A Requesting Data...1816523079</v>
         <stp/>
         <stp>BDP|318717744080343059</stp>
         <tr r="D160" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...844228604</v>
+        <v>#N/A Requesting Data...2256317831</v>
         <stp/>
         <stp>BDP|906890884136209558</stp>
         <tr r="D292" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4208440875</v>
+        <v>#N/A Requesting Data...1637404942</v>
         <stp/>
         <stp>BDP|201374897063670414</stp>
         <tr r="D523" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1587856733</v>
+        <v>#N/A Requesting Data...3428600137</v>
         <stp/>
         <stp>BDP|531076695287606366</stp>
         <tr r="D400" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3634543605</v>
+        <v>#N/A Requesting Data...1584893612</v>
         <stp/>
         <stp>BDP|144477032269742222</stp>
         <tr r="D441" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3098603263</v>
+        <v>#N/A Requesting Data...3724132630</v>
         <stp/>
         <stp>BDP|369335997283767693</stp>
         <tr r="D42" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3961540706</v>
+        <v>#N/A Requesting Data...2243481055</v>
         <stp/>
         <stp>BDP|397864705266572167</stp>
         <tr r="D167" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1112117593</v>
+        <v>#N/A Requesting Data...1807354863</v>
         <stp/>
         <stp>BDP|311302696366017280</stp>
         <tr r="D203" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1615198921</v>
+        <v>#N/A Requesting Data...3345191574</v>
         <stp/>
         <stp>BDP|233898526081711550</stp>
         <tr r="D490" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1501749497</v>
+        <v>#N/A Requesting Data...1829307433</v>
         <stp/>
         <stp>BDP|922369095513489762</stp>
         <tr r="D568" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1179165930</v>
+        <v>#N/A Requesting Data...2688377832</v>
         <stp/>
         <stp>BDP|979275311794530914</stp>
         <tr r="D473" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3948847276</v>
+        <v>#N/A Requesting Data...1508607554</v>
         <stp/>
         <stp>BDP|143898849454240623</stp>
         <tr r="D240" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3318955391</v>
+        <v>#N/A Requesting Data...1413244850</v>
         <stp/>
         <stp>BDP|346782390500645557</stp>
         <tr r="D447" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4192006190</v>
+        <v>#N/A Requesting Data...3125897888</v>
         <stp/>
         <stp>BDP|797189529280801998</stp>
         <tr r="D572" s="1"/>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="D2">
         <f>_xll.BDP(C2,"PX_CLOSE")</f>
-        <v>2.2799999999999998</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="D3">
         <f>_xll.BDP(C3,"PX_CLOSE")</f>
-        <v>14.97</v>
+        <v>16.350000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="D4">
         <f>_xll.BDP(C4,"PX_CLOSE")</f>
-        <v>79.98</v>
+        <v>97.24</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="D5">
         <f>_xll.BDP(C5,"PX_CLOSE")</f>
-        <v>38.29</v>
+        <v>37.24</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="D6">
         <f>_xll.BDP(C6,"PX_CLOSE")</f>
-        <v>46.61</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="D7">
         <f>_xll.BDP(C7,"PX_CLOSE")</f>
-        <v>106.75</v>
+        <v>125.54</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D8">
         <f>_xll.BDP(C8,"PX_CLOSE")</f>
-        <v>17.649999999999999</v>
+        <v>21.58</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D9">
         <f>_xll.BDP(C9,"PX_CLOSE")</f>
-        <v>1.1399999999999999</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D10">
         <f>_xll.BDP(C10,"PX_CLOSE")</f>
-        <v>13.87</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="D11">
         <f>_xll.BDP(C11,"PX_CLOSE")</f>
-        <v>53.66</v>
+        <v>61.12</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="D12">
         <f>_xll.BDP(C12,"PX_CLOSE")</f>
-        <v>10.17</v>
+        <v>12.74</v>
       </c>
       <c r="L12" s="1"/>
     </row>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="D13">
         <f>_xll.BDP(C13,"PX_CLOSE")</f>
-        <v>7.79</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="D14">
         <f>_xll.BDP(C14,"PX_CLOSE")</f>
-        <v>22.11</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="D15">
         <f>_xll.BDP(C15,"PX_CLOSE")</f>
-        <v>5.03</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="D16">
         <f>_xll.BDP(C16,"PX_CLOSE")</f>
-        <v>10.75</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="D17">
         <f>_xll.BDP(C17,"PX_CLOSE")</f>
-        <v>77.73</v>
+        <v>84.82</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="D18">
         <f>_xll.BDP(C18,"PX_CLOSE")</f>
-        <v>15.38</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D19">
         <f>_xll.BDP(C19,"PX_CLOSE")</f>
-        <v>16.38</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="D20">
         <f>_xll.BDP(C20,"PX_CLOSE")</f>
-        <v>40.97</v>
+        <v>45.88</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="D21">
         <f>_xll.BDP(C21,"PX_CLOSE")</f>
-        <v>103.9</v>
+        <v>131.86000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="D22">
         <f>_xll.BDP(C22,"PX_CLOSE")</f>
-        <v>7.03</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -6103,9 +6103,9 @@
         <f t="shared" si="0"/>
         <v>AXIA6 BZ Equity</v>
       </c>
-      <c r="D23" t="str">
+      <c r="D23">
         <f>_xll.BDP(C23,"PX_CLOSE")</f>
-        <v>#N/A N/A</v>
+        <v>59.19</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="D24">
         <f>_xll.BDP(C24,"PX_CLOSE")</f>
-        <v>4.3600000000000003</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="D25">
         <f>_xll.BDP(C25,"PX_CLOSE")</f>
-        <v>42.2</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="D26">
         <f>_xll.BDP(C26,"PX_CLOSE")</f>
-        <v>22.65</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="D27">
         <f>_xll.BDP(C27,"PX_CLOSE")</f>
-        <v>14.26</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="D28">
         <f>_xll.BDP(C28,"PX_CLOSE")</f>
-        <v>36.159999999999997</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="D29">
         <f>_xll.BDP(C29,"PX_CLOSE")</f>
-        <v>34.25</v>
+        <v>37.46</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="D30">
         <f>_xll.BDP(C30,"PX_CLOSE")</f>
-        <v>28.47</v>
+        <v>143.54</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="D31">
         <f>_xll.BDP(C31,"PX_CLOSE")</f>
-        <v>27.41</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="D32">
         <f>_xll.BDP(C32,"PX_CLOSE")</f>
-        <v>52.7</v>
+        <v>75.209999999999994</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="D33">
         <f>_xll.BDP(C33,"PX_CLOSE")</f>
-        <v>15.4</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D34">
         <f>_xll.BDP(C34,"PX_CLOSE")</f>
-        <v>0.42</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="D35">
         <f>_xll.BDP(C35,"PX_CLOSE")</f>
-        <v>13.05</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="D36">
         <f>_xll.BDP(C36,"PX_CLOSE")</f>
-        <v>13.43</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="D37">
         <f>_xll.BDP(C37,"PX_CLOSE")</f>
-        <v>3.7</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D38">
         <f>_xll.BDP(C38,"PX_CLOSE")</f>
-        <v>3.57</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D39">
         <f>_xll.BDP(C39,"PX_CLOSE")</f>
-        <v>9.0399999999999991</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="D40">
         <f>_xll.BDP(C40,"PX_CLOSE")</f>
-        <v>54.1</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D41">
         <f>_xll.BDP(C41,"PX_CLOSE")</f>
-        <v>21.38</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="D42">
         <f>_xll.BDP(C42,"PX_CLOSE")</f>
-        <v>38.68</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="D43">
         <f>_xll.BDP(C43,"PX_CLOSE")</f>
-        <v>4.2699999999999996</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="D44">
         <f>_xll.BDP(C44,"PX_CLOSE")</f>
-        <v>19.73</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D45">
         <f>_xll.BDP(C45,"PX_CLOSE")</f>
-        <v>22.18</v>
+        <v>24.66</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="D46">
         <f>_xll.BDP(C46,"PX_CLOSE")</f>
-        <v>9.99</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="D47">
         <f>_xll.BDP(C47,"PX_CLOSE")</f>
-        <v>37.21</v>
+        <v>46.59</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="D48">
         <f>_xll.BDP(C48,"PX_CLOSE")</f>
-        <v>19.41</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="D49">
         <f>_xll.BDP(C49,"PX_CLOSE")</f>
-        <v>26.38</v>
+        <v>36.82</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="D50">
         <f>_xll.BDP(C50,"PX_CLOSE")</f>
-        <v>17.57</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="D51">
         <f>_xll.BDP(C51,"PX_CLOSE")</f>
-        <v>16.850000000000001</v>
+        <v>16.079999999999998</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="D52">
         <f>_xll.BDP(C52,"PX_CLOSE")</f>
-        <v>4.3499999999999996</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="D53">
         <f>_xll.BDP(C53,"PX_CLOSE")</f>
-        <v>39.72</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="D54">
         <f>_xll.BDP(C54,"PX_CLOSE")</f>
-        <v>3.82</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="D55">
         <f>_xll.BDP(C55,"PX_CLOSE")</f>
-        <v>1.42</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="D56">
         <f>_xll.BDP(C56,"PX_CLOSE")</f>
-        <v>13.65</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="D57">
         <f>_xll.BDP(C57,"PX_CLOSE")</f>
-        <v>0.55000000000000004</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D58">
         <f>_xll.BDP(C58,"PX_CLOSE")</f>
-        <v>42.8</v>
+        <v>39.590000000000003</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D59">
         <f>_xll.BDP(C59,"PX_CLOSE")</f>
-        <v>52.38</v>
+        <v>51.76</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="D60">
         <f>_xll.BDP(C60,"PX_CLOSE")</f>
-        <v>7.81</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="D61">
         <f>_xll.BDP(C61,"PX_CLOSE")</f>
-        <v>5.01</v>
+        <v>8.2799999999999994</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="D62">
         <f>_xll.BDP(C62,"PX_CLOSE")</f>
-        <v>3.94</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="D63">
         <f>_xll.BDP(C63,"PX_CLOSE")</f>
-        <v>1.37</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="D64">
         <f>_xll.BDP(C64,"PX_CLOSE")</f>
-        <v>9.56</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="D65">
         <f>_xll.BDP(C65,"PX_CLOSE")</f>
-        <v>14.26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="D66">
         <f>_xll.BDP(C66,"PX_CLOSE")</f>
-        <v>19</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="D67">
         <f>_xll.BDP(C67,"PX_CLOSE")</f>
-        <v>14.5</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="D68">
         <f>_xll.BDP(C68,"PX_CLOSE")</f>
-        <v>16.14</v>
+        <v>18.87</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="D69">
         <f>_xll.BDP(C69,"PX_CLOSE")</f>
-        <v>11.21</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D70">
         <f>_xll.BDP(C70,"PX_CLOSE")</f>
-        <v>13.12</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D71">
         <f>_xll.BDP(C71,"PX_CLOSE")</f>
-        <v>107.21</v>
+        <v>106.09</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="D72">
         <f>_xll.BDP(C72,"PX_CLOSE")</f>
-        <v>0.17</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="D73">
         <f>_xll.BDP(C73,"PX_CLOSE")</f>
-        <v>4.28</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="D74">
         <f>_xll.BDP(C74,"PX_CLOSE")</f>
-        <v>19.309999999999999</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="D75">
         <f>_xll.BDP(C75,"PX_CLOSE")</f>
-        <v>27.05</v>
+        <v>31.27</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="D76">
         <f>_xll.BDP(C76,"PX_CLOSE")</f>
-        <v>54.18</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="D77">
         <f>_xll.BDP(C77,"PX_CLOSE")</f>
-        <v>8.27</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="D78">
         <f>_xll.BDP(C78,"PX_CLOSE")</f>
-        <v>2.11</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="D79">
         <f>_xll.BDP(C79,"PX_CLOSE")</f>
-        <v>14.72</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="D80">
         <f>_xll.BDP(C80,"PX_CLOSE")</f>
-        <v>8.68</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="D81">
         <f>_xll.BDP(C81,"PX_CLOSE")</f>
-        <v>21.15</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="D82">
         <f>_xll.BDP(C82,"PX_CLOSE")</f>
-        <v>18.920000000000002</v>
+        <v>25.15</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="D83">
         <f>_xll.BDP(C83,"PX_CLOSE")</f>
-        <v>167.61</v>
+        <v>179.2</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="D84">
         <f>_xll.BDP(C84,"PX_CLOSE")</f>
-        <v>10.96</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D85">
         <f>_xll.BDP(C85,"PX_CLOSE")</f>
-        <v>27.3</v>
+        <v>28.48</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="D86">
         <f>_xll.BDP(C86,"PX_CLOSE")</f>
-        <v>24.56</v>
+        <v>28.59</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D87">
         <f>_xll.BDP(C87,"PX_CLOSE")</f>
-        <v>63.49</v>
+        <v>82.24</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="D88">
         <f>_xll.BDP(C88,"PX_CLOSE")</f>
-        <v>41.76</v>
+        <v>49.57</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="D89">
         <f>_xll.BDP(C89,"PX_CLOSE")</f>
-        <v>175.98</v>
+        <v>187.95</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="D90">
         <f>_xll.BDP(C90,"PX_CLOSE")</f>
-        <v>12.98</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="D91">
         <f>_xll.BDP(C91,"PX_CLOSE")</f>
-        <v>8.7799999999999994</v>
+        <v>14.49</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="D92">
         <f>_xll.BDP(C92,"PX_CLOSE")</f>
-        <v>9.31</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="D93">
         <f>_xll.BDP(C93,"PX_CLOSE")</f>
-        <v>44.37</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="D94">
         <f>_xll.BDP(C94,"PX_CLOSE")</f>
-        <v>3.41</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="D95">
         <f>_xll.BDP(C95,"PX_CLOSE")</f>
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="D96">
         <f>_xll.BDP(C96,"PX_CLOSE")</f>
-        <v>56.4</v>
+        <v>58.11</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D97">
         <f>_xll.BDP(C97,"PX_CLOSE")</f>
-        <v>197.7</v>
+        <v>273.47000000000003</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="D98">
         <f>_xll.BDP(C98,"PX_CLOSE")</f>
-        <v>13.37</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="D99">
         <f>_xll.BDP(C99,"PX_CLOSE")</f>
-        <v>29.11</v>
+        <v>29.62</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="D100">
         <f>_xll.BDP(C100,"PX_CLOSE")</f>
-        <v>64.64</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="D101">
         <f>_xll.BDP(C101,"PX_CLOSE")</f>
-        <v>2.77</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="D102">
         <f>_xll.BDP(C102,"PX_CLOSE")</f>
-        <v>10.68</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="D103">
         <f>_xll.BDP(C103,"PX_CLOSE")</f>
-        <v>76.739999999999995</v>
+        <v>68.87</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="D104">
         <f>_xll.BDP(C104,"PX_CLOSE")</f>
-        <v>18.72</v>
+        <v>16.059999999999999</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="D105">
         <f>_xll.BDP(C105,"PX_CLOSE")</f>
-        <v>17.079999999999998</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="D106">
         <f>_xll.BDP(C106,"PX_CLOSE")</f>
-        <v>10.72</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="D107">
         <f>_xll.BDP(C107,"PX_CLOSE")</f>
-        <v>25.32</v>
+        <v>25.87</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="D108">
         <f>_xll.BDP(C108,"PX_CLOSE")</f>
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D109">
         <f>_xll.BDP(C109,"PX_CLOSE")</f>
-        <v>52.99</v>
+        <v>54</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="D110">
         <f>_xll.BDP(C110,"PX_CLOSE")</f>
-        <v>4.9000000000000004</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="D111">
         <f>_xll.BDP(C111,"PX_CLOSE")</f>
-        <v>31</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="D112">
         <f>_xll.BDP(C112,"PX_CLOSE")</f>
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -7543,9 +7543,9 @@
         <f t="shared" si="1"/>
         <v>GUAR3 BZ Equity</v>
       </c>
-      <c r="D113" t="str">
+      <c r="D113">
         <f>_xll.BDP(C113,"PX_CLOSE")</f>
-        <v>#N/A N/A</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="D114">
         <f>_xll.BDP(C114,"PX_CLOSE")</f>
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -7575,9 +7575,9 @@
         <f t="shared" si="1"/>
         <v>AZUL53 BZ Equity</v>
       </c>
-      <c r="D115" t="str">
+      <c r="D115">
         <f>_xll.BDP(C115,"PX_CLOSE")</f>
-        <v>#N/A N/A</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="D116">
         <f>_xll.BDP(C116,"PX_CLOSE")</f>
-        <v>56.5</v>
+        <v>88.79</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D117">
         <f>_xll.BDP(C117,"PX_CLOSE")</f>
-        <v>79.84</v>
+        <v>92.95</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="D118">
         <f>_xll.BDP(C118,"PX_CLOSE")</f>
-        <v>38</v>
+        <v>40.950000000000003</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="D119">
         <f>_xll.BDP(C119,"PX_CLOSE")</f>
-        <v>11.18</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="D120">
         <f>_xll.BDP(C120,"PX_CLOSE")</f>
-        <v>10.78</v>
+        <v>9.7799999999999994</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="D121">
         <f>_xll.BDP(C121,"PX_CLOSE")</f>
-        <v>22.5</v>
+        <v>30.63</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D122">
         <f>_xll.BDP(C122,"PX_CLOSE")</f>
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="D123">
         <f>_xll.BDP(C123,"PX_CLOSE")</f>
-        <v>3.78</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="D124">
         <f>_xll.BDP(C124,"PX_CLOSE")</f>
-        <v>11.23</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="D125">
         <f>_xll.BDP(C125,"PX_CLOSE")</f>
-        <v>2.63</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="D126">
         <f>_xll.BDP(C126,"PX_CLOSE")</f>
-        <v>63.85</v>
+        <v>65.650000000000006</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="D127">
         <f>_xll.BDP(C127,"PX_CLOSE")</f>
-        <v>149.38</v>
+        <v>150.68</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="D128">
         <f>_xll.BDP(C128,"PX_CLOSE")</f>
-        <v>5.49</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="D129">
         <f>_xll.BDP(C129,"PX_CLOSE")</f>
-        <v>38.49</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="D130">
         <f>_xll.BDP(C130,"PX_CLOSE")</f>
-        <v>33.6</v>
+        <v>33.51</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="D131">
         <f>_xll.BDP(C131,"PX_CLOSE")</f>
-        <v>46.4</v>
+        <v>50.64</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="D132">
         <f>_xll.BDP(C132,"PX_CLOSE")</f>
-        <v>20.99</v>
+        <v>25.41</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="D133">
         <f>_xll.BDP(C133,"PX_CLOSE")</f>
-        <v>27.83</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="D134">
         <f>_xll.BDP(C134,"PX_CLOSE")</f>
-        <v>5.0599999999999996</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="D135">
         <f>_xll.BDP(C135,"PX_CLOSE")</f>
-        <v>5.83</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="D136">
         <f>_xll.BDP(C136,"PX_CLOSE")</f>
-        <v>16.850000000000001</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="D137">
         <f>_xll.BDP(C137,"PX_CLOSE")</f>
-        <v>76.400000000000006</v>
+        <v>71.180000000000007</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="D138">
         <f>_xll.BDP(C138,"PX_CLOSE")</f>
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="D139">
         <f>_xll.BDP(C139,"PX_CLOSE")</f>
-        <v>20.52</v>
+        <v>24.37</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="D140">
         <f>_xll.BDP(C140,"PX_CLOSE")</f>
-        <v>6.01</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="D141">
         <f>_xll.BDP(C141,"PX_CLOSE")</f>
-        <v>12.25</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="D142">
         <f>_xll.BDP(C142,"PX_CLOSE")</f>
-        <v>59.73</v>
+        <v>63.73</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="D143">
         <f>_xll.BDP(C143,"PX_CLOSE")</f>
-        <v>12.02</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="D144">
         <f>_xll.BDP(C144,"PX_CLOSE")</f>
-        <v>26.5</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="D145">
         <f>_xll.BDP(C145,"PX_CLOSE")</f>
-        <v>3.6</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="D146">
         <f>_xll.BDP(C146,"PX_CLOSE")</f>
-        <v>15.36</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="D147">
         <f>_xll.BDP(C147,"PX_CLOSE")</f>
-        <v>6.61</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="D148">
         <f>_xll.BDP(C148,"PX_CLOSE")</f>
-        <v>54.48</v>
+        <v>59.39</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D149">
         <f>_xll.BDP(C149,"PX_CLOSE")</f>
-        <v>18.77</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="D150">
         <f>_xll.BDP(C150,"PX_CLOSE")</f>
-        <v>7.62</v>
+        <v>9.0500000000000007</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="D151">
         <f>_xll.BDP(C151,"PX_CLOSE")</f>
-        <v>138.25</v>
+        <v>141.69</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="D152">
         <f>_xll.BDP(C152,"PX_CLOSE")</f>
-        <v>25.94</v>
+        <v>21</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="D153">
         <f>_xll.BDP(C153,"PX_CLOSE")</f>
-        <v>63.5</v>
+        <v>61.81</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="D154">
         <f>_xll.BDP(C154,"PX_CLOSE")</f>
-        <v>115</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="D155">
         <f>_xll.BDP(C155,"PX_CLOSE")</f>
-        <v>925</v>
+        <v>385.01</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="D156">
         <f>_xll.BDP(C156,"PX_CLOSE")</f>
-        <v>2250</v>
+        <v>627.9</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="D157">
         <f>_xll.BDP(C157,"PX_CLOSE")</f>
-        <v>11.68</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -8263,9 +8263,9 @@
         <f t="shared" si="2"/>
         <v>ODPV3 BZ Equity</v>
       </c>
-      <c r="D158" t="str">
+      <c r="D158">
         <f>_xll.BDP(C158,"PX_CLOSE")</f>
-        <v>#N/A N/A</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="D159">
         <f>_xll.BDP(C159,"PX_CLOSE")</f>
-        <v>3.89</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="D160">
         <f>_xll.BDP(C160,"PX_CLOSE")</f>
-        <v>14.21</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="D161">
         <f>_xll.BDP(C161,"PX_CLOSE")</f>
-        <v>21.02</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D162">
         <f>_xll.BDP(C162,"PX_CLOSE")</f>
-        <v>1.37</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="D163">
         <f>_xll.BDP(C163,"PX_CLOSE")</f>
-        <v>10.59</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="D164">
         <f>_xll.BDP(C164,"PX_CLOSE")</f>
-        <v>77.67</v>
+        <v>75.33</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="D165">
         <f>_xll.BDP(C165,"PX_CLOSE")</f>
-        <v>14.84</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="D166">
         <f>_xll.BDP(C166,"PX_CLOSE")</f>
-        <v>10</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="D167">
         <f>_xll.BDP(C167,"PX_CLOSE")</f>
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="D168">
         <f>_xll.BDP(C168,"PX_CLOSE")</f>
-        <v>17.68</v>
+        <v>18.059999999999999</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="D169">
         <f>_xll.BDP(C169,"PX_CLOSE")</f>
-        <v>3.85</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="D170">
         <f>_xll.BDP(C170,"PX_CLOSE")</f>
-        <v>32.67</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="D171">
         <f>_xll.BDP(C171,"PX_CLOSE")</f>
-        <v>17.96</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="D172">
         <f>_xll.BDP(C172,"PX_CLOSE")</f>
-        <v>17.46</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="D173">
         <f>_xll.BDP(C173,"PX_CLOSE")</f>
-        <v>15.02</v>
+        <v>13.19</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="D174">
         <f>_xll.BDP(C174,"PX_CLOSE")</f>
-        <v>34.1</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="D175">
         <f>_xll.BDP(C175,"PX_CLOSE")</f>
-        <v>15.16</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="D176">
         <f>_xll.BDP(C176,"PX_CLOSE")</f>
-        <v>103.3</v>
+        <v>110</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="D177">
         <f>_xll.BDP(C177,"PX_CLOSE")</f>
-        <v>32.25</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="D178">
         <f>_xll.BDP(C178,"PX_CLOSE")</f>
-        <v>13.1</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="D179">
         <f>_xll.BDP(C179,"PX_CLOSE")</f>
-        <v>58.28</v>
+        <v>52.38</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="D180">
         <f>_xll.BDP(C180,"PX_CLOSE")</f>
-        <v>7.12</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="D181">
         <f>_xll.BDP(C181,"PX_CLOSE")</f>
-        <v>52.35</v>
+        <v>69.069999999999993</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="D182">
         <f>_xll.BDP(C182,"PX_CLOSE")</f>
-        <v>7.65</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="D183">
         <f>_xll.BDP(C183,"PX_CLOSE")</f>
-        <v>1.27</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D184">
         <f>_xll.BDP(C184,"PX_CLOSE")</f>
-        <v>2.59</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="D185">
         <f>_xll.BDP(C185,"PX_CLOSE")</f>
-        <v>90</v>
+        <v>126.31</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="D186">
         <f>_xll.BDP(C186,"PX_CLOSE")</f>
-        <v>72.28</v>
+        <v>94.97</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="D187">
         <f>_xll.BDP(C187,"PX_CLOSE")</f>
-        <v>13.3</v>
+        <v>18.600000000000001</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="D188">
         <f>_xll.BDP(C188,"PX_CLOSE")</f>
-        <v>40.33</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="D189">
         <f>_xll.BDP(C189,"PX_CLOSE")</f>
-        <v>34.96</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="D190">
         <f>_xll.BDP(C190,"PX_CLOSE")</f>
-        <v>12.7</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="D191">
         <f>_xll.BDP(C191,"PX_CLOSE")</f>
-        <v>21.52</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="D192">
         <f>_xll.BDP(C192,"PX_CLOSE")</f>
-        <v>39.74</v>
+        <v>48.71</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="D193">
         <f>_xll.BDP(C193,"PX_CLOSE")</f>
-        <v>43.3</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D194">
         <f>_xll.BDP(C194,"PX_CLOSE")</f>
-        <v>27.72</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="D195">
         <f>_xll.BDP(C195,"PX_CLOSE")</f>
-        <v>40.11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="D196">
         <f>_xll.BDP(C196,"PX_CLOSE")</f>
-        <v>69.989999999999995</v>
+        <v>66.14</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="D197">
         <f>_xll.BDP(C197,"PX_CLOSE")</f>
-        <v>28.85</v>
+        <v>32.869999999999997</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="D198">
         <f>_xll.BDP(C198,"PX_CLOSE")</f>
-        <v>23.08</v>
+        <v>24.89</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="D199">
         <f>_xll.BDP(C199,"PX_CLOSE")</f>
-        <v>0.08</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="D200">
         <f>_xll.BDP(C200,"PX_CLOSE")</f>
-        <v>4.95</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="D201">
         <f>_xll.BDP(C201,"PX_CLOSE")</f>
-        <v>3.16</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="D202">
         <f>_xll.BDP(C202,"PX_CLOSE")</f>
-        <v>5.96</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="D203">
         <f>_xll.BDP(C203,"PX_CLOSE")</f>
-        <v>1.53</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="D204">
         <f>_xll.BDP(C204,"PX_CLOSE")</f>
-        <v>42.27</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="D205">
         <f>_xll.BDP(C205,"PX_CLOSE")</f>
-        <v>91</v>
+        <v>72.02</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="D206">
         <f>_xll.BDP(C206,"PX_CLOSE")</f>
-        <v>193.84</v>
+        <v>184.28</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="D207">
         <f>_xll.BDP(C207,"PX_CLOSE")</f>
-        <v>33.5</v>
+        <v>40.47</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="D208">
         <f>_xll.BDP(C208,"PX_CLOSE")</f>
-        <v>22.2</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="D209">
         <f>_xll.BDP(C209,"PX_CLOSE")</f>
-        <v>8.15</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="D210">
         <f>_xll.BDP(C210,"PX_CLOSE")</f>
-        <v>12.82</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="D211">
         <f>_xll.BDP(C211,"PX_CLOSE")</f>
-        <v>60.78</v>
+        <v>64.16</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="D212">
         <f>_xll.BDP(C212,"PX_CLOSE")</f>
-        <v>30.75</v>
+        <v>31.68</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="D213">
         <f>_xll.BDP(C213,"PX_CLOSE")</f>
-        <v>81.88</v>
+        <v>104.09</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="D214">
         <f>_xll.BDP(C214,"PX_CLOSE")</f>
-        <v>0.28000000000000003</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="D215">
         <f>_xll.BDP(C215,"PX_CLOSE")</f>
-        <v>8.56</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="D216">
         <f>_xll.BDP(C216,"PX_CLOSE")</f>
-        <v>431</v>
+        <v>412.2</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="D217">
         <f>_xll.BDP(C217,"PX_CLOSE")</f>
-        <v>6.03</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="D218">
         <f>_xll.BDP(C218,"PX_CLOSE")</f>
-        <v>4.1500000000000004</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="D219">
         <f>_xll.BDP(C219,"PX_CLOSE")</f>
-        <v>28.92</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="D220">
         <f>_xll.BDP(C220,"PX_CLOSE")</f>
-        <v>174.68</v>
+        <v>186.98</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="D221">
         <f>_xll.BDP(C221,"PX_CLOSE")</f>
-        <v>2.85</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="D222">
         <f>_xll.BDP(C222,"PX_CLOSE")</f>
-        <v>5.61</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="D223">
         <f>_xll.BDP(C223,"PX_CLOSE")</f>
-        <v>10.98</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="D224">
         <f>_xll.BDP(C224,"PX_CLOSE")</f>
-        <v>23.65</v>
+        <v>20.89</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="D225">
         <f>_xll.BDP(C225,"PX_CLOSE")</f>
-        <v>101.4</v>
+        <v>102.56</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="D226">
         <f>_xll.BDP(C226,"PX_CLOSE")</f>
-        <v>5.56</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="D227">
         <f>_xll.BDP(C227,"PX_CLOSE")</f>
-        <v>91.21</v>
+        <v>94.36</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="D228">
         <f>_xll.BDP(C228,"PX_CLOSE")</f>
-        <v>3</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="D229">
         <f>_xll.BDP(C229,"PX_CLOSE")</f>
-        <v>90.22</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="D230">
         <f>_xll.BDP(C230,"PX_CLOSE")</f>
-        <v>77.87</v>
+        <v>88.08</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="D231">
         <f>_xll.BDP(C231,"PX_CLOSE")</f>
-        <v>8.6</v>
+        <v>8.0399999999999991</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="D232">
         <f>_xll.BDP(C232,"PX_CLOSE")</f>
-        <v>88.2</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="D233">
         <f>_xll.BDP(C233,"PX_CLOSE")</f>
-        <v>47.9</v>
+        <v>55.06</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="D234">
         <f>_xll.BDP(C234,"PX_CLOSE")</f>
-        <v>149.11000000000001</v>
+        <v>161.72</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="D235">
         <f>_xll.BDP(C235,"PX_CLOSE")</f>
-        <v>3.95</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="D236">
         <f>_xll.BDP(C236,"PX_CLOSE")</f>
-        <v>91.75</v>
+        <v>90.43</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="D237">
         <f>_xll.BDP(C237,"PX_CLOSE")</f>
-        <v>0.61</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="D238">
         <f>_xll.BDP(C238,"PX_CLOSE")</f>
-        <v>67.5</v>
+        <v>75.400000000000006</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="D239">
         <f>_xll.BDP(C239,"PX_CLOSE")</f>
-        <v>91.5</v>
+        <v>97.17</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="D240">
         <f>_xll.BDP(C240,"PX_CLOSE")</f>
-        <v>71.849999999999994</v>
+        <v>76.260000000000005</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="D241">
         <f>_xll.BDP(C241,"PX_CLOSE")</f>
-        <v>8.99</v>
+        <v>9.36</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="D242">
         <f>_xll.BDP(C242,"PX_CLOSE")</f>
-        <v>88.4</v>
+        <v>94</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="D243">
         <f>_xll.BDP(C243,"PX_CLOSE")</f>
-        <v>4.83</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="D244">
         <f>_xll.BDP(C244,"PX_CLOSE")</f>
-        <v>1.84</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="D245">
         <f>_xll.BDP(C245,"PX_CLOSE")</f>
-        <v>84.99</v>
+        <v>93.99</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="D246">
         <f>_xll.BDP(C246,"PX_CLOSE")</f>
-        <v>6.43</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="D247">
         <f>_xll.BDP(C247,"PX_CLOSE")</f>
-        <v>149.80000000000001</v>
+        <v>156.91999999999999</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="D248">
         <f>_xll.BDP(C248,"PX_CLOSE")</f>
-        <v>19.3</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="D249">
         <f>_xll.BDP(C249,"PX_CLOSE")</f>
-        <v>6.13</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="D250">
         <f>_xll.BDP(C250,"PX_CLOSE")</f>
-        <v>8.76</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="D251">
         <f>_xll.BDP(C251,"PX_CLOSE")</f>
-        <v>126.68</v>
+        <v>123.65</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="D252">
         <f>_xll.BDP(C252,"PX_CLOSE")</f>
-        <v>10.84</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="D253">
         <f>_xll.BDP(C253,"PX_CLOSE")</f>
-        <v>1</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D254">
         <f>_xll.BDP(C254,"PX_CLOSE")</f>
-        <v>8.65</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="D255">
         <f>_xll.BDP(C255,"PX_CLOSE")</f>
-        <v>103.01</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="D256">
         <f>_xll.BDP(C256,"PX_CLOSE")</f>
-        <v>103.43</v>
+        <v>110.83</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="D257">
         <f>_xll.BDP(C257,"PX_CLOSE")</f>
-        <v>9.08</v>
+        <v>8.89</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="D258">
         <f>_xll.BDP(C258,"PX_CLOSE")</f>
-        <v>99.5</v>
+        <v>99.01</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D259">
         <f>_xll.BDP(C259,"PX_CLOSE")</f>
-        <v>62</v>
+        <v>72.099999999999994</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="D260">
         <f>_xll.BDP(C260,"PX_CLOSE")</f>
-        <v>25.19</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="D261">
         <f>_xll.BDP(C261,"PX_CLOSE")</f>
-        <v>151.15</v>
+        <v>160.91999999999999</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="D262">
         <f>_xll.BDP(C262,"PX_CLOSE")</f>
-        <v>121.57</v>
+        <v>132.57</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="D263">
         <f>_xll.BDP(C263,"PX_CLOSE")</f>
-        <v>88.69</v>
+        <v>90.77</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="D264">
         <f>_xll.BDP(C264,"PX_CLOSE")</f>
-        <v>142.85</v>
+        <v>152.71</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="D265">
         <f>_xll.BDP(C265,"PX_CLOSE")</f>
-        <v>9.83</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="D266">
         <f>_xll.BDP(C266,"PX_CLOSE")</f>
-        <v>39.51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="D267">
         <f>_xll.BDP(C267,"PX_CLOSE")</f>
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="D268">
         <f>_xll.BDP(C268,"PX_CLOSE")</f>
-        <v>128.51</v>
+        <v>128</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="D269">
         <f>_xll.BDP(C269,"PX_CLOSE")</f>
-        <v>101.28</v>
+        <v>93</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="D270">
         <f>_xll.BDP(C270,"PX_CLOSE")</f>
-        <v>123.45</v>
+        <v>130.82</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="D271">
         <f>_xll.BDP(C271,"PX_CLOSE")</f>
-        <v>3.37</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="D272">
         <f>_xll.BDP(C272,"PX_CLOSE")</f>
-        <v>0.94</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="D273">
         <f>_xll.BDP(C273,"PX_CLOSE")</f>
-        <v>61</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="D274">
         <f>_xll.BDP(C274,"PX_CLOSE")</f>
-        <v>7.85</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="D275">
         <f>_xll.BDP(C275,"PX_CLOSE")</f>
-        <v>17.16</v>
+        <v>22.11</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="D276">
         <f>_xll.BDP(C276,"PX_CLOSE")</f>
-        <v>11</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="D277">
         <f>_xll.BDP(C277,"PX_CLOSE")</f>
-        <v>15.39</v>
+        <v>15.53</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="D278">
         <f>_xll.BDP(C278,"PX_CLOSE")</f>
-        <v>5.22</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
@@ -10201,7 +10201,7 @@
       </c>
       <c r="D279">
         <f>_xll.BDP(C279,"PX_CLOSE")</f>
-        <v>58.34</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="D280">
         <f>_xll.BDP(C280,"PX_CLOSE")</f>
-        <v>21.52</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="D281">
         <f>_xll.BDP(C281,"PX_CLOSE")</f>
-        <v>3.29</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="D282">
         <f>_xll.BDP(C282,"PX_CLOSE")</f>
-        <v>17.5</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="D283">
         <f>_xll.BDP(C283,"PX_CLOSE")</f>
-        <v>6.93</v>
+        <v>8.39</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -10279,9 +10279,9 @@
         <f t="shared" si="4"/>
         <v>GOLL54 BZ Equity</v>
       </c>
-      <c r="D284" t="str">
+      <c r="D284">
         <f>_xll.BDP(C284,"PX_CLOSE")</f>
-        <v>#N/A N/A</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="D285">
         <f>_xll.BDP(C285,"PX_CLOSE")</f>
-        <v>23.81</v>
+        <v>35.49</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="D286">
         <f>_xll.BDP(C286,"PX_CLOSE")</f>
-        <v>71.02</v>
+        <v>64.959999999999994</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="D287">
         <f>_xll.BDP(C287,"PX_CLOSE")</f>
-        <v>7.17</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="D288">
         <f>_xll.BDP(C288,"PX_CLOSE")</f>
-        <v>6</v>
+        <v>8.3800000000000008</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="D289">
         <f>_xll.BDP(C289,"PX_CLOSE")</f>
-        <v>15.3</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="D290">
         <f>_xll.BDP(C290,"PX_CLOSE")</f>
-        <v>99.35</v>
+        <v>105.74</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="D291">
         <f>_xll.BDP(C291,"PX_CLOSE")</f>
-        <v>8.6199999999999992</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="D292">
         <f>_xll.BDP(C292,"PX_CLOSE")</f>
-        <v>173.68</v>
+        <v>162.29</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="D293">
         <f>_xll.BDP(C293,"PX_CLOSE")</f>
-        <v>11.32</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="D294">
         <f>_xll.BDP(C294,"PX_CLOSE")</f>
-        <v>70.39</v>
+        <v>93.24</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="D295">
         <f>_xll.BDP(C295,"PX_CLOSE")</f>
-        <v>18.510000000000002</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="D296">
         <f>_xll.BDP(C296,"PX_CLOSE")</f>
-        <v>3.64</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="D297">
         <f>_xll.BDP(C297,"PX_CLOSE")</f>
-        <v>340</v>
+        <v>162.81</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -10505,7 +10505,7 @@
       </c>
       <c r="D298">
         <f>_xll.BDP(C298,"PX_CLOSE")</f>
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="D299">
         <f>_xll.BDP(C299,"PX_CLOSE")</f>
-        <v>3.37</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D300">
         <f>_xll.BDP(C300,"PX_CLOSE")</f>
-        <v>9.68</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="D301">
         <f>_xll.BDP(C301,"PX_CLOSE")</f>
-        <v>24.03</v>
+        <v>27.18</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="D302">
         <f>_xll.BDP(C302,"PX_CLOSE")</f>
-        <v>7.76</v>
+        <v>8.4700000000000006</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="D303">
         <f>_xll.BDP(C303,"PX_CLOSE")</f>
-        <v>13.22</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="D304">
         <f>_xll.BDP(C304,"PX_CLOSE")</f>
-        <v>2.06</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="D305">
         <f>_xll.BDP(C305,"PX_CLOSE")</f>
-        <v>103.15</v>
+        <v>108.26</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="D306">
         <f>_xll.BDP(C306,"PX_CLOSE")</f>
-        <v>11.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="D307">
         <f>_xll.BDP(C307,"PX_CLOSE")</f>
-        <v>6</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="D308">
         <f>_xll.BDP(C308,"PX_CLOSE")</f>
-        <v>8.93</v>
+        <v>9.8800000000000008</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D309">
         <f>_xll.BDP(C309,"PX_CLOSE")</f>
-        <v>14.55</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D310">
         <f>_xll.BDP(C310,"PX_CLOSE")</f>
-        <v>90.37</v>
+        <v>98.09</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="D311">
         <f>_xll.BDP(C311,"PX_CLOSE")</f>
-        <v>7.39</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="D312">
         <f>_xll.BDP(C312,"PX_CLOSE")</f>
-        <v>92.74</v>
+        <v>100.72</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="D313">
         <f>_xll.BDP(C313,"PX_CLOSE")</f>
-        <v>9.6999999999999993</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="D314">
         <f>_xll.BDP(C314,"PX_CLOSE")</f>
-        <v>18.41</v>
+        <v>19.22</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="D315">
         <f>_xll.BDP(C315,"PX_CLOSE")</f>
-        <v>51.07</v>
+        <v>78.45</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="D316">
         <f>_xll.BDP(C316,"PX_CLOSE")</f>
-        <v>6.42</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="D317">
         <f>_xll.BDP(C317,"PX_CLOSE")</f>
-        <v>12.17</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D318">
         <f>_xll.BDP(C318,"PX_CLOSE")</f>
-        <v>128.06</v>
+        <v>147.27000000000001</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="D319">
         <f>_xll.BDP(C319,"PX_CLOSE")</f>
-        <v>9.02</v>
+        <v>9.64</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="D320">
         <f>_xll.BDP(C320,"PX_CLOSE")</f>
-        <v>4.7300000000000004</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="D321">
         <f>_xll.BDP(C321,"PX_CLOSE")</f>
-        <v>9.9499999999999993</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="D322">
         <f>_xll.BDP(C322,"PX_CLOSE")</f>
-        <v>13.79</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="D323">
         <f>_xll.BDP(C323,"PX_CLOSE")</f>
-        <v>5.8</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="D324">
         <f>_xll.BDP(C324,"PX_CLOSE")</f>
-        <v>7.68</v>
+        <v>10.220000000000001</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="D325">
         <f>_xll.BDP(C325,"PX_CLOSE")</f>
-        <v>3.67</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -10951,9 +10951,9 @@
         <f t="shared" si="5"/>
         <v>NEOE3 BZ Equity</v>
       </c>
-      <c r="D326" t="str">
+      <c r="D326">
         <f>_xll.BDP(C326,"PX_CLOSE")</f>
-        <v>#N/A N/A</v>
+        <v>32.450000000000003</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D327">
         <f>_xll.BDP(C327,"PX_CLOSE")</f>
-        <v>30.45</v>
+        <v>39.880000000000003</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="D328">
         <f>_xll.BDP(C328,"PX_CLOSE")</f>
-        <v>2.19</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="D329">
         <f>_xll.BDP(C329,"PX_CLOSE")</f>
-        <v>288.93</v>
+        <v>226.3</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="D330">
         <f>_xll.BDP(C330,"PX_CLOSE")</f>
-        <v>111.7</v>
+        <v>104.35</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="D331">
         <f>_xll.BDP(C331,"PX_CLOSE")</f>
-        <v>4.7300000000000004</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="D332">
         <f>_xll.BDP(C332,"PX_CLOSE")</f>
-        <v>9.64</v>
+        <v>9.9499999999999993</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="D333">
         <f>_xll.BDP(C333,"PX_CLOSE")</f>
-        <v>30.1</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="D334">
         <f>_xll.BDP(C334,"PX_CLOSE")</f>
-        <v>6.36</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="D335">
         <f>_xll.BDP(C335,"PX_CLOSE")</f>
-        <v>130.46</v>
+        <v>170.77</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D336">
         <f>_xll.BDP(C336,"PX_CLOSE")</f>
-        <v>7.68</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="D337">
         <f>_xll.BDP(C337,"PX_CLOSE")</f>
-        <v>10.39</v>
+        <v>9.6199999999999992</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="D338">
         <f>_xll.BDP(C338,"PX_CLOSE")</f>
-        <v>8.2200000000000006</v>
+        <v>8.7100000000000009</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="D339">
         <f>_xll.BDP(C339,"PX_CLOSE")</f>
-        <v>7.49</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="D340">
         <f>_xll.BDP(C340,"PX_CLOSE")</f>
-        <v>125</v>
+        <v>119.8</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="D341">
         <f>_xll.BDP(C341,"PX_CLOSE")</f>
-        <v>2.73</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="D342">
         <f>_xll.BDP(C342,"PX_CLOSE")</f>
-        <v>79</v>
+        <v>81.89</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="D343">
         <f>_xll.BDP(C343,"PX_CLOSE")</f>
-        <v>5.91</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="D344">
         <f>_xll.BDP(C344,"PX_CLOSE")</f>
-        <v>35.36</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D345">
         <f>_xll.BDP(C345,"PX_CLOSE")</f>
-        <v>34.200000000000003</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="D346">
         <f>_xll.BDP(C346,"PX_CLOSE")</f>
-        <v>4.8600000000000003</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="D347">
         <f>_xll.BDP(C347,"PX_CLOSE")</f>
-        <v>110.11</v>
+        <v>130.07</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="D348">
         <f>_xll.BDP(C348,"PX_CLOSE")</f>
-        <v>55.45</v>
+        <v>65.349999999999994</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="D349">
         <f>_xll.BDP(C349,"PX_CLOSE")</f>
-        <v>4.43</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="D350">
         <f>_xll.BDP(C350,"PX_CLOSE")</f>
-        <v>95.77</v>
+        <v>91.94</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="D351">
         <f>_xll.BDP(C351,"PX_CLOSE")</f>
-        <v>201.65</v>
+        <v>162.58000000000001</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="D352">
         <f>_xll.BDP(C352,"PX_CLOSE")</f>
-        <v>0.64</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="D353">
         <f>_xll.BDP(C353,"PX_CLOSE")</f>
-        <v>7.03</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D354">
         <f>_xll.BDP(C354,"PX_CLOSE")</f>
-        <v>187.3</v>
+        <v>166.52</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="D355">
         <f>_xll.BDP(C355,"PX_CLOSE")</f>
-        <v>4.13</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="D356">
         <f>_xll.BDP(C356,"PX_CLOSE")</f>
-        <v>0.83</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="D357">
         <f>_xll.BDP(C357,"PX_CLOSE")</f>
-        <v>57.24</v>
+        <v>58</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="D358">
         <f>_xll.BDP(C358,"PX_CLOSE")</f>
-        <v>13.27</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="D359">
         <f>_xll.BDP(C359,"PX_CLOSE")</f>
-        <v>10.199999999999999</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="D360">
         <f>_xll.BDP(C360,"PX_CLOSE")</f>
-        <v>145.11000000000001</v>
+        <v>138.4</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="D361">
         <f>_xll.BDP(C361,"PX_CLOSE")</f>
-        <v>59.21</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="D362">
         <f>_xll.BDP(C362,"PX_CLOSE")</f>
-        <v>43.02</v>
+        <v>39.950000000000003</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D363">
         <f>_xll.BDP(C363,"PX_CLOSE")</f>
-        <v>13.33</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="D364">
         <f>_xll.BDP(C364,"PX_CLOSE")</f>
-        <v>76</v>
+        <v>93.29</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="D365">
         <f>_xll.BDP(C365,"PX_CLOSE")</f>
-        <v>379.37</v>
+        <v>212.11</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="D366">
         <f>_xll.BDP(C366,"PX_CLOSE")</f>
-        <v>0.44</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="D367">
         <f>_xll.BDP(C367,"PX_CLOSE")</f>
-        <v>483.06</v>
+        <v>592.17999999999995</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="D368">
         <f>_xll.BDP(C368,"PX_CLOSE")</f>
-        <v>53.55</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="D369">
         <f>_xll.BDP(C369,"PX_CLOSE")</f>
-        <v>37.64</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="D370">
         <f>_xll.BDP(C370,"PX_CLOSE")</f>
-        <v>47.29</v>
+        <v>51.13</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="D371">
         <f>_xll.BDP(C371,"PX_CLOSE")</f>
-        <v>152.72</v>
+        <v>140.91</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D372">
         <f>_xll.BDP(C372,"PX_CLOSE")</f>
-        <v>477.26</v>
+        <v>504.27</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="D373">
         <f>_xll.BDP(C373,"PX_CLOSE")</f>
-        <v>165.75</v>
+        <v>137.63999999999999</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="D374">
         <f>_xll.BDP(C374,"PX_CLOSE")</f>
-        <v>71.349999999999994</v>
+        <v>83.83</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="D375">
         <f>_xll.BDP(C375,"PX_CLOSE")</f>
-        <v>89.41</v>
+        <v>91.62</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="D376">
         <f>_xll.BDP(C376,"PX_CLOSE")</f>
-        <v>50.8</v>
+        <v>62.49</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="D377">
         <f>_xll.BDP(C377,"PX_CLOSE")</f>
-        <v>86.86</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="D378">
         <f>_xll.BDP(C378,"PX_CLOSE")</f>
-        <v>129.1</v>
+        <v>126.25</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="D379">
         <f>_xll.BDP(C379,"PX_CLOSE")</f>
-        <v>7.26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="D380">
         <f>_xll.BDP(C380,"PX_CLOSE")</f>
-        <v>39.65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D381">
         <f>_xll.BDP(C381,"PX_CLOSE")</f>
-        <v>13.3</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="D382">
         <f>_xll.BDP(C382,"PX_CLOSE")</f>
-        <v>3.04</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="D383">
         <f>_xll.BDP(C383,"PX_CLOSE")</f>
-        <v>79.34</v>
+        <v>89.48</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="D384">
         <f>_xll.BDP(C384,"PX_CLOSE")</f>
-        <v>28.15</v>
+        <v>29.86</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="D385">
         <f>_xll.BDP(C385,"PX_CLOSE")</f>
-        <v>59.1</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="D386">
         <f>_xll.BDP(C386,"PX_CLOSE")</f>
-        <v>22.92</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="D387">
         <f>_xll.BDP(C387,"PX_CLOSE")</f>
-        <v>2.72</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="D388">
         <f>_xll.BDP(C388,"PX_CLOSE")</f>
-        <v>42.4</v>
+        <v>46.82</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="D389">
         <f>_xll.BDP(C389,"PX_CLOSE")</f>
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
@@ -11975,9 +11975,9 @@
         <f t="shared" si="6"/>
         <v>USAL11 BZ Equity</v>
       </c>
-      <c r="D390" t="str">
+      <c r="D390">
         <f>_xll.BDP(C390,"PX_CLOSE")</f>
-        <v>#N/A N/A</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="D391">
         <f>_xll.BDP(C391,"PX_CLOSE")</f>
-        <v>129</v>
+        <v>113.89</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="D392">
         <f>_xll.BDP(C392,"PX_CLOSE")</f>
-        <v>25.28</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="D393">
         <f>_xll.BDP(C393,"PX_CLOSE")</f>
-        <v>93.6</v>
+        <v>134.68</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="D394">
         <f>_xll.BDP(C394,"PX_CLOSE")</f>
-        <v>75.52</v>
+        <v>76.37</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="D395">
         <f>_xll.BDP(C395,"PX_CLOSE")</f>
-        <v>51.72</v>
+        <v>68.349999999999994</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="D396">
         <f>_xll.BDP(C396,"PX_CLOSE")</f>
-        <v>78.48</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="D397">
         <f>_xll.BDP(C397,"PX_CLOSE")</f>
-        <v>164.35</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="D398">
         <f>_xll.BDP(C398,"PX_CLOSE")</f>
-        <v>137.5</v>
+        <v>121.86</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="D399">
         <f>_xll.BDP(C399,"PX_CLOSE")</f>
-        <v>4.01</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="D400">
         <f>_xll.BDP(C400,"PX_CLOSE")</f>
-        <v>71.819999999999993</v>
+        <v>90.06</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="D401">
         <f>_xll.BDP(C401,"PX_CLOSE")</f>
-        <v>48.35</v>
+        <v>105.16</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="D402">
         <f>_xll.BDP(C402,"PX_CLOSE")</f>
-        <v>37.47</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D403">
         <f>_xll.BDP(C403,"PX_CLOSE")</f>
-        <v>21.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="D404">
         <f>_xll.BDP(C404,"PX_CLOSE")</f>
-        <v>6.35</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="D405">
         <f>_xll.BDP(C405,"PX_CLOSE")</f>
-        <v>215.04</v>
+        <v>201</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="D406">
         <f>_xll.BDP(C406,"PX_CLOSE")</f>
-        <v>240.48</v>
+        <v>329.8</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="D407">
         <f>_xll.BDP(C407,"PX_CLOSE")</f>
-        <v>192.48</v>
+        <v>164.51</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="D408">
         <f>_xll.BDP(C408,"PX_CLOSE")</f>
-        <v>564.74</v>
+        <v>537.47</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="D409">
         <f>_xll.BDP(C409,"PX_CLOSE")</f>
-        <v>44.4</v>
+        <v>40.64</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="D410">
         <f>_xll.BDP(C410,"PX_CLOSE")</f>
-        <v>286.44</v>
+        <v>252.45</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="D411">
         <f>_xll.BDP(C411,"PX_CLOSE")</f>
-        <v>606.79</v>
+        <v>608.20000000000005</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="D412">
         <f>_xll.BDP(C412,"PX_CLOSE")</f>
-        <v>61.38</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="D413">
         <f>_xll.BDP(C413,"PX_CLOSE")</f>
-        <v>40.56</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="D414">
         <f>_xll.BDP(C414,"PX_CLOSE")</f>
-        <v>109.5</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="D415">
         <f>_xll.BDP(C415,"PX_CLOSE")</f>
-        <v>7.82</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D416">
         <f>_xll.BDP(C416,"PX_CLOSE")</f>
-        <v>995.18</v>
+        <v>973.5</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="D417">
         <f>_xll.BDP(C417,"PX_CLOSE")</f>
-        <v>5119.2</v>
+        <v>2256.42</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="D418">
         <f>_xll.BDP(C418,"PX_CLOSE")</f>
-        <v>60.75</v>
+        <v>65.069999999999993</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="D419">
         <f>_xll.BDP(C419,"PX_CLOSE")</f>
-        <v>108.46</v>
+        <v>90.36</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="D420">
         <f>_xll.BDP(C420,"PX_CLOSE")</f>
-        <v>162.08000000000001</v>
+        <v>156.6</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="D421">
         <f>_xll.BDP(C421,"PX_CLOSE")</f>
-        <v>50.5</v>
+        <v>59.64</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="D422">
         <f>_xll.BDP(C422,"PX_CLOSE")</f>
-        <v>12.06</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="D423">
         <f>_xll.BDP(C423,"PX_CLOSE")</f>
-        <v>58.5</v>
+        <v>62.13</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="D424">
         <f>_xll.BDP(C424,"PX_CLOSE")</f>
-        <v>46.39</v>
+        <v>28.29</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D425">
         <f>_xll.BDP(C425,"PX_CLOSE")</f>
-        <v>177.84</v>
+        <v>207.06</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="D426">
         <f>_xll.BDP(C426,"PX_CLOSE")</f>
-        <v>29.88</v>
+        <v>38.58</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="D427">
         <f>_xll.BDP(C427,"PX_CLOSE")</f>
-        <v>47.91</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="D428">
         <f>_xll.BDP(C428,"PX_CLOSE")</f>
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="D429">
         <f>_xll.BDP(C429,"PX_CLOSE")</f>
-        <v>78.88</v>
+        <v>80.64</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="D430">
         <f>_xll.BDP(C430,"PX_CLOSE")</f>
-        <v>101.9</v>
+        <v>130.02000000000001</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="D431">
         <f>_xll.BDP(C431,"PX_CLOSE")</f>
-        <v>49.49</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="D432">
         <f>_xll.BDP(C432,"PX_CLOSE")</f>
-        <v>107.99</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="D433">
         <f>_xll.BDP(C433,"PX_CLOSE")</f>
-        <v>60</v>
+        <v>77.75</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D434">
         <f>_xll.BDP(C434,"PX_CLOSE")</f>
-        <v>97.73</v>
+        <v>97.99</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
@@ -12697,7 +12697,7 @@
       </c>
       <c r="D435">
         <f>_xll.BDP(C435,"PX_CLOSE")</f>
-        <v>58</v>
+        <v>60.59</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="D436">
         <f>_xll.BDP(C436,"PX_CLOSE")</f>
-        <v>109.89</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="D437">
         <f>_xll.BDP(C437,"PX_CLOSE")</f>
-        <v>177.66</v>
+        <v>175.68</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="D438">
         <f>_xll.BDP(C438,"PX_CLOSE")</f>
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="D439">
         <f>_xll.BDP(C439,"PX_CLOSE")</f>
-        <v>127.79</v>
+        <v>136.88999999999999</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
@@ -12777,7 +12777,7 @@
       </c>
       <c r="D440">
         <f>_xll.BDP(C440,"PX_CLOSE")</f>
-        <v>8.5</v>
+        <v>8.2799999999999994</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="D441">
         <f>_xll.BDP(C441,"PX_CLOSE")</f>
-        <v>51.8</v>
+        <v>52.97</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="D442">
         <f>_xll.BDP(C442,"PX_CLOSE")</f>
-        <v>271.89</v>
+        <v>200</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D443">
         <f>_xll.BDP(C443,"PX_CLOSE")</f>
-        <v>5.13</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="D444">
         <f>_xll.BDP(C444,"PX_CLOSE")</f>
-        <v>32.369999999999997</v>
+        <v>33.51</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.25">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="D445">
         <f>_xll.BDP(C445,"PX_CLOSE")</f>
-        <v>423.12</v>
+        <v>383.86</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="D446">
         <f>_xll.BDP(C446,"PX_CLOSE")</f>
-        <v>49.4</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="D447">
         <f>_xll.BDP(C447,"PX_CLOSE")</f>
-        <v>78.56</v>
+        <v>88.81</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="D448">
         <f>_xll.BDP(C448,"PX_CLOSE")</f>
-        <v>81.22</v>
+        <v>81.28</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="D449">
         <f>_xll.BDP(C449,"PX_CLOSE")</f>
-        <v>64.02</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="D450">
         <f>_xll.BDP(C450,"PX_CLOSE")</f>
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="D451">
         <f>_xll.BDP(C451,"PX_CLOSE")</f>
-        <v>44.37</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D452">
         <f>_xll.BDP(C452,"PX_CLOSE")</f>
-        <v>133.77000000000001</v>
+        <v>95.9</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="D453">
         <f>_xll.BDP(C453,"PX_CLOSE")</f>
-        <v>107.19</v>
+        <v>110.58</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="D454">
         <f>_xll.BDP(C454,"PX_CLOSE")</f>
-        <v>79.91</v>
+        <v>77.010000000000005</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="D455">
         <f>_xll.BDP(C455,"PX_CLOSE")</f>
-        <v>39.08</v>
+        <v>39.409999999999997</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="D456">
         <f>_xll.BDP(C456,"PX_CLOSE")</f>
-        <v>54.18</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="D457">
         <f>_xll.BDP(C457,"PX_CLOSE")</f>
-        <v>34</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="D458">
         <f>_xll.BDP(C458,"PX_CLOSE")</f>
-        <v>159.04</v>
+        <v>149</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="D459">
         <f>_xll.BDP(C459,"PX_CLOSE")</f>
-        <v>65.34</v>
+        <v>64.45</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="D460">
         <f>_xll.BDP(C460,"PX_CLOSE")</f>
-        <v>36.64</v>
+        <v>41</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D461">
         <f>_xll.BDP(C461,"PX_CLOSE")</f>
-        <v>9.5500000000000007</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="D462">
         <f>_xll.BDP(C462,"PX_CLOSE")</f>
-        <v>93.87</v>
+        <v>84.65</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
@@ -13145,7 +13145,7 @@
       </c>
       <c r="D463">
         <f>_xll.BDP(C463,"PX_CLOSE")</f>
-        <v>9.3800000000000008</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="D464">
         <f>_xll.BDP(C464,"PX_CLOSE")</f>
-        <v>77.28</v>
+        <v>76.23</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="D465">
         <f>_xll.BDP(C465,"PX_CLOSE")</f>
-        <v>107.14</v>
+        <v>106.54</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="D466">
         <f>_xll.BDP(C466,"PX_CLOSE")</f>
-        <v>16.5</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="D467">
         <f>_xll.BDP(C467,"PX_CLOSE")</f>
-        <v>13.31</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="D468">
         <f>_xll.BDP(C468,"PX_CLOSE")</f>
-        <v>397.02</v>
+        <v>390</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="D469">
         <f>_xll.BDP(C469,"PX_CLOSE")</f>
-        <v>15.14</v>
+        <v>30.72</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D470">
         <f>_xll.BDP(C470,"PX_CLOSE")</f>
-        <v>68.81</v>
+        <v>73.849999999999994</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="D471">
         <f>_xll.BDP(C471,"PX_CLOSE")</f>
-        <v>52.3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="D472">
         <f>_xll.BDP(C472,"PX_CLOSE")</f>
-        <v>61.99</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="D473">
         <f>_xll.BDP(C473,"PX_CLOSE")</f>
-        <v>62.52</v>
+        <v>56.49</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="D474">
         <f>_xll.BDP(C474,"PX_CLOSE")</f>
-        <v>4.82</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="D475">
         <f>_xll.BDP(C475,"PX_CLOSE")</f>
-        <v>46.58</v>
+        <v>44.58</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="D476">
         <f>_xll.BDP(C476,"PX_CLOSE")</f>
-        <v>114.72</v>
+        <v>129.13999999999999</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="D477">
         <f>_xll.BDP(C477,"PX_CLOSE")</f>
-        <v>93.18</v>
+        <v>109.32</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="D478">
         <f>_xll.BDP(C478,"PX_CLOSE")</f>
-        <v>2.78</v>
+        <v>4.5199999999999996</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="D479">
         <f>_xll.BDP(C479,"PX_CLOSE")</f>
-        <v>124.57</v>
+        <v>124.77</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="D480">
         <f>_xll.BDP(C480,"PX_CLOSE")</f>
-        <v>49.34</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="D481">
         <f>_xll.BDP(C481,"PX_CLOSE")</f>
-        <v>151.35</v>
+        <v>170.88</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="D482">
         <f>_xll.BDP(C482,"PX_CLOSE")</f>
-        <v>29.55</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D483">
         <f>_xll.BDP(C483,"PX_CLOSE")</f>
-        <v>61.26</v>
+        <v>63.31</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="D484">
         <f>_xll.BDP(C484,"PX_CLOSE")</f>
-        <v>52.48</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="D485">
         <f>_xll.BDP(C485,"PX_CLOSE")</f>
-        <v>82.4</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="D486">
         <f>_xll.BDP(C486,"PX_CLOSE")</f>
-        <v>35.24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="D487">
         <f>_xll.BDP(C487,"PX_CLOSE")</f>
-        <v>124.32</v>
+        <v>165.91</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="D488">
         <f>_xll.BDP(C488,"PX_CLOSE")</f>
-        <v>50.1</v>
+        <v>54.65</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="D489">
         <f>_xll.BDP(C489,"PX_CLOSE")</f>
-        <v>59.22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.25">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="D490">
         <f>_xll.BDP(C490,"PX_CLOSE")</f>
-        <v>37.94</v>
+        <v>40.32</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="D491">
         <f>_xll.BDP(C491,"PX_CLOSE")</f>
-        <v>132.99</v>
+        <v>135</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D492">
         <f>_xll.BDP(C492,"PX_CLOSE")</f>
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="D493">
         <f>_xll.BDP(C493,"PX_CLOSE")</f>
-        <v>88.88</v>
+        <v>75.099999999999994</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="D494">
         <f>_xll.BDP(C494,"PX_CLOSE")</f>
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="D495">
         <f>_xll.BDP(C495,"PX_CLOSE")</f>
-        <v>48.1</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
@@ -13673,7 +13673,7 @@
       </c>
       <c r="D496">
         <f>_xll.BDP(C496,"PX_CLOSE")</f>
-        <v>41.81</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="D497">
         <f>_xll.BDP(C497,"PX_CLOSE")</f>
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="D498">
         <f>_xll.BDP(C498,"PX_CLOSE")</f>
-        <v>60.18</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="D499">
         <f>_xll.BDP(C499,"PX_CLOSE")</f>
-        <v>99.48</v>
+        <v>114.43</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="D500">
         <f>_xll.BDP(C500,"PX_CLOSE")</f>
-        <v>17.78</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D501">
         <f>_xll.BDP(C501,"PX_CLOSE")</f>
-        <v>40</v>
+        <v>48.11</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="D502">
         <f>_xll.BDP(C502,"PX_CLOSE")</f>
-        <v>57.48</v>
+        <v>51.15</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="D503">
         <f>_xll.BDP(C503,"PX_CLOSE")</f>
-        <v>52.72</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
@@ -13801,7 +13801,7 @@
       </c>
       <c r="D504">
         <f>_xll.BDP(C504,"PX_CLOSE")</f>
-        <v>16.920000000000002</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="D505">
         <f>_xll.BDP(C505,"PX_CLOSE")</f>
-        <v>112.88</v>
+        <v>117.9</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="D506">
         <f>_xll.BDP(C506,"PX_CLOSE")</f>
-        <v>52.41</v>
+        <v>50.28</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="D507">
         <f>_xll.BDP(C507,"PX_CLOSE")</f>
-        <v>31.15</v>
+        <v>34.799999999999997</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="D508">
         <f>_xll.BDP(C508,"PX_CLOSE")</f>
-        <v>542.72</v>
+        <v>481.92</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
@@ -13881,7 +13881,7 @@
       </c>
       <c r="D509">
         <f>_xll.BDP(C509,"PX_CLOSE")</f>
-        <v>3.51</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="D510">
         <f>_xll.BDP(C510,"PX_CLOSE")</f>
-        <v>44.29</v>
+        <v>38.549999999999997</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.25">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="D511">
         <f>_xll.BDP(C511,"PX_CLOSE")</f>
-        <v>11.33</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="D512">
         <f>_xll.BDP(C512,"PX_CLOSE")</f>
-        <v>38.590000000000003</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.25">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="D513">
         <f>_xll.BDP(C513,"PX_CLOSE")</f>
-        <v>180.5</v>
+        <v>180.49</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.25">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="D514">
         <f>_xll.BDP(C514,"PX_CLOSE")</f>
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.25">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="D515">
         <f>_xll.BDP(C515,"PX_CLOSE")</f>
-        <v>0.13</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.25">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="D516">
         <f>_xll.BDP(C516,"PX_CLOSE")</f>
-        <v>25.84</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.25">
@@ -14009,7 +14009,7 @@
       </c>
       <c r="D517">
         <f>_xll.BDP(C517,"PX_CLOSE")</f>
-        <v>83.83</v>
+        <v>94.63</v>
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.25">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="D518">
         <f>_xll.BDP(C518,"PX_CLOSE")</f>
-        <v>21.5</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="D519">
         <f>_xll.BDP(C519,"PX_CLOSE")</f>
-        <v>19.27</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
@@ -14057,7 +14057,7 @@
       </c>
       <c r="D520">
         <f>_xll.BDP(C520,"PX_CLOSE")</f>
-        <v>136.28</v>
+        <v>139</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="D521">
         <f>_xll.BDP(C521,"PX_CLOSE")</f>
-        <v>160.68</v>
+        <v>104.01</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.25">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="D522">
         <f>_xll.BDP(C522,"PX_CLOSE")</f>
-        <v>28.35</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="D523">
         <f>_xll.BDP(C523,"PX_CLOSE")</f>
-        <v>39.64</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="D524">
         <f>_xll.BDP(C524,"PX_CLOSE")</f>
-        <v>20.56</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="D525">
         <f>_xll.BDP(C525,"PX_CLOSE")</f>
-        <v>3.19</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="D526">
         <f>_xll.BDP(C526,"PX_CLOSE")</f>
-        <v>11.69</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.25">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="D527">
         <f>_xll.BDP(C527,"PX_CLOSE")</f>
-        <v>18.21</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="D528">
         <f>_xll.BDP(C528,"PX_CLOSE")</f>
-        <v>12.95</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="D529">
         <f>_xll.BDP(C529,"PX_CLOSE")</f>
-        <v>59.79</v>
+        <v>68.319999999999993</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="D530">
         <f>_xll.BDP(C530,"PX_CLOSE")</f>
-        <v>60.92</v>
+        <v>68.95</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="D531">
         <f>_xll.BDP(C531,"PX_CLOSE")</f>
-        <v>93.6</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.25">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="D532">
         <f>_xll.BDP(C532,"PX_CLOSE")</f>
-        <v>5.83</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
@@ -14265,7 +14265,7 @@
       </c>
       <c r="D533">
         <f>_xll.BDP(C533,"PX_CLOSE")</f>
-        <v>17.89</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
@@ -14281,7 +14281,7 @@
       </c>
       <c r="D534">
         <f>_xll.BDP(C534,"PX_CLOSE")</f>
-        <v>1.18</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="D535">
         <f>_xll.BDP(C535,"PX_CLOSE")</f>
-        <v>139.75</v>
+        <v>138.91999999999999</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D536">
         <f>_xll.BDP(C536,"PX_CLOSE")</f>
-        <v>10.029999999999999</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.25">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="D537">
         <f>_xll.BDP(C537,"PX_CLOSE")</f>
-        <v>62.72</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="D538">
         <f>_xll.BDP(C538,"PX_CLOSE")</f>
-        <v>140.54</v>
+        <v>149.72</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="D539">
         <f>_xll.BDP(C539,"PX_CLOSE")</f>
-        <v>80.05</v>
+        <v>82.68</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.25">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="D540">
         <f>_xll.BDP(C540,"PX_CLOSE")</f>
-        <v>38.74</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="D541">
         <f>_xll.BDP(C541,"PX_CLOSE")</f>
-        <v>9.6</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="D542">
         <f>_xll.BDP(C542,"PX_CLOSE")</f>
-        <v>33.5</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="D543">
         <f>_xll.BDP(C543,"PX_CLOSE")</f>
-        <v>211.47</v>
+        <v>184.17</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="D544">
         <f>_xll.BDP(C544,"PX_CLOSE")</f>
-        <v>15.18</v>
+        <v>18.87</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D545">
         <f>_xll.BDP(C545,"PX_CLOSE")</f>
-        <v>26.15</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.25">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="D546">
         <f>_xll.BDP(C546,"PX_CLOSE")</f>
-        <v>1.7</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.25">
@@ -14489,7 +14489,7 @@
       </c>
       <c r="D547">
         <f>_xll.BDP(C547,"PX_CLOSE")</f>
-        <v>122.52</v>
+        <v>131.9</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="D548">
         <f>_xll.BDP(C548,"PX_CLOSE")</f>
-        <v>18.989999999999998</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.25">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="D549">
         <f>_xll.BDP(C549,"PX_CLOSE")</f>
-        <v>82.54</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="D550">
         <f>_xll.BDP(C550,"PX_CLOSE")</f>
-        <v>27.86</v>
+        <v>38.75</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="D551">
         <f>_xll.BDP(C551,"PX_CLOSE")</f>
-        <v>99</v>
+        <v>100.03</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.25">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="D552">
         <f>_xll.BDP(C552,"PX_CLOSE")</f>
-        <v>115.81</v>
+        <v>67.819999999999993</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.25">
@@ -14585,7 +14585,7 @@
       </c>
       <c r="D553">
         <f>_xll.BDP(C553,"PX_CLOSE")</f>
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.25">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="D554">
         <f>_xll.BDP(C554,"PX_CLOSE")</f>
-        <v>123.95</v>
+        <v>142.56</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.25">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="D555">
         <f>_xll.BDP(C555,"PX_CLOSE")</f>
-        <v>37.619999999999997</v>
+        <v>54.15</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.25">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="D556">
         <f>_xll.BDP(C556,"PX_CLOSE")</f>
-        <v>8.57</v>
+        <v>9.14</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="D557">
         <f>_xll.BDP(C557,"PX_CLOSE")</f>
-        <v>21.86</v>
+        <v>33</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.25">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="D558">
         <f>_xll.BDP(C558,"PX_CLOSE")</f>
-        <v>0.93</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="D559">
         <f>_xll.BDP(C559,"PX_CLOSE")</f>
-        <v>0.98</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.25">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="D560">
         <f>_xll.BDP(C560,"PX_CLOSE")</f>
-        <v>229.77</v>
+        <v>213.59</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.25">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="D561">
         <f>_xll.BDP(C561,"PX_CLOSE")</f>
-        <v>86.8</v>
+        <v>91.89</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.25">
@@ -14729,7 +14729,7 @@
       </c>
       <c r="D562">
         <f>_xll.BDP(C562,"PX_CLOSE")</f>
-        <v>9.68</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.25">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="D563">
         <f>_xll.BDP(C563,"PX_CLOSE")</f>
-        <v>6.36</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.25">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="D564">
         <f>_xll.BDP(C564,"PX_CLOSE")</f>
-        <v>53.25</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.25">
@@ -14777,7 +14777,7 @@
       </c>
       <c r="D565">
         <f>_xll.BDP(C565,"PX_CLOSE")</f>
-        <v>9.74</v>
+        <v>10.050000000000001</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.25">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="D566">
         <f>_xll.BDP(C566,"PX_CLOSE")</f>
-        <v>110.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="D567">
         <f>_xll.BDP(C567,"PX_CLOSE")</f>
-        <v>52.24</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.25">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="D568">
         <f>_xll.BDP(C568,"PX_CLOSE")</f>
-        <v>60.8</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.25">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="D569">
         <f>_xll.BDP(C569,"PX_CLOSE")</f>
-        <v>5.4</v>
+        <v>154.08000000000001</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.25">
@@ -14857,7 +14857,7 @@
       </c>
       <c r="D570">
         <f>_xll.BDP(C570,"PX_CLOSE")</f>
-        <v>73.06</v>
+        <v>86.23</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.25">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="D571">
         <f>_xll.BDP(C571,"PX_CLOSE")</f>
-        <v>71.760000000000005</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.25">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="D572">
         <f>_xll.BDP(C572,"PX_CLOSE")</f>
-        <v>15.79</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.25">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="D573">
         <f>_xll.BDP(C573,"PX_CLOSE")</f>
-        <v>8.01</v>
+        <v>8.7200000000000006</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.25">
@@ -14921,7 +14921,7 @@
       </c>
       <c r="D574">
         <f>_xll.BDP(C574,"PX_CLOSE")</f>
-        <v>171.72</v>
+        <v>194.5</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.25">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="D575">
         <f>_xll.BDP(C575,"PX_CLOSE")</f>
-        <v>6.17</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.25">
@@ -14951,9 +14951,9 @@
         <f t="shared" si="8"/>
         <v>PATL11 BZ Equity</v>
       </c>
-      <c r="D576" t="str">
+      <c r="D576">
         <f>_xll.BDP(C576,"PX_CLOSE")</f>
-        <v>#N/A N/A</v>
+        <v>66</v>
       </c>
     </row>
     <row r="577" spans="1:17" x14ac:dyDescent="0.25">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="D577">
         <f>_xll.BDP(C577,"PX_CLOSE")</f>
-        <v>136.88</v>
+        <v>139.01</v>
       </c>
     </row>
     <row r="578" spans="1:17" x14ac:dyDescent="0.25">
@@ -14985,7 +14985,7 @@
       </c>
       <c r="D578">
         <f>_xll.BDP(C578,"PX_CLOSE")</f>
-        <v>8.3699999999999992</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="579" spans="1:17" x14ac:dyDescent="0.25">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="D579">
         <f>_xll.BDP(C579,"PX_CLOSE")</f>
-        <v>253.5</v>
+        <v>270.92</v>
       </c>
     </row>
     <row r="580" spans="1:17" x14ac:dyDescent="0.25">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="D580">
         <f>_xll.BDP(C580,"PX_CLOSE")</f>
-        <v>31.19</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="581" spans="1:17" x14ac:dyDescent="0.25">
@@ -15033,7 +15033,7 @@
       </c>
       <c r="D581">
         <f>_xll.BDP(C581,"PX_CLOSE")</f>
-        <v>78.56</v>
+        <v>74.459999999999994</v>
       </c>
     </row>
     <row r="582" spans="1:17" x14ac:dyDescent="0.25">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="D582">
         <f>_xll.BDP(C582,"PX_CLOSE")</f>
-        <v>78.3</v>
+        <v>78.680000000000007</v>
       </c>
     </row>
     <row r="583" spans="1:17" x14ac:dyDescent="0.25">
@@ -15065,7 +15065,7 @@
       </c>
       <c r="D583">
         <f>_xll.BDP(C583,"PX_CLOSE")</f>
-        <v>7.13</v>
+        <v>8.7100000000000009</v>
       </c>
     </row>
     <row r="584" spans="1:17" x14ac:dyDescent="0.25">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="D584">
         <f>_xll.BDP(C584,"PX_CLOSE")</f>
-        <v>159.04</v>
+        <v>166.02</v>
       </c>
       <c r="Q584" s="1"/>
     </row>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="D585">
         <f>_xll.BDP(C585,"PX_CLOSE")</f>
-        <v>2.23</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="586" spans="1:17" x14ac:dyDescent="0.25">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="D586">
         <f>_xll.BDP(C586,"PX_CLOSE")</f>
-        <v>56.6</v>
+        <v>64.25</v>
       </c>
     </row>
     <row r="587" spans="1:17" x14ac:dyDescent="0.25">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="D587">
         <f>_xll.BDP(C587,"PX_CLOSE")</f>
-        <v>9.09</v>
+        <v>8.3699999999999992</v>
       </c>
     </row>
     <row r="588" spans="1:17" x14ac:dyDescent="0.25">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="D588">
         <f>_xll.BDP(C588,"PX_CLOSE")</f>
-        <v>129.13</v>
+        <v>79.67</v>
       </c>
     </row>
     <row r="589" spans="1:17" x14ac:dyDescent="0.25">
@@ -15162,7 +15162,7 @@
       </c>
       <c r="D589">
         <f>_xll.BDP(C589,"PX_CLOSE")</f>
-        <v>117.2</v>
+        <v>129.72999999999999</v>
       </c>
     </row>
   </sheetData>
